--- a/output/ARKF/00_Starter_Residual_1_to_2.5pct/ARKF_starter_residual_analysis.xlsx
+++ b/output/ARKF/00_Starter_Residual_1_to_2.5pct/ARKF_starter_residual_analysis.xlsx
@@ -534,31 +534,31 @@
         <v>51.85185185185185</v>
       </c>
       <c r="G2" t="n">
-        <v>426.037037037037</v>
+        <v>432.2592592592592</v>
       </c>
       <c r="H2" t="n">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I2" t="n">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>85.57993730407524</v>
+        <v>85.57692307692307</v>
       </c>
       <c r="M2" t="n">
-        <v>88.15047021943573</v>
+        <v>93.69871794871794</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>280</v>
+        <v>668.1</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +663,7 @@
         <v>3.507531832285647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9893952372926909</v>
+        <v>0.8927311657534539</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>1.404166302449437</v>
       </c>
       <c r="E7" t="n">
-        <v>1.197690784147578</v>
+        <v>1.218916357119191</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="H7" t="n">
-        <v>178</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
@@ -813,7 +813,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="E8" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         <v>1.292460305251573</v>
       </c>
       <c r="D9" t="n">
-        <v>1.292460305251573</v>
+        <v>1.574130368246454</v>
       </c>
       <c r="E9" t="n">
-        <v>1.12629414570516</v>
+        <v>1.459023472686469</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -870,10 +870,10 @@
         <v>1.559371968450113</v>
       </c>
       <c r="D10" t="n">
-        <v>3.142034401757555</v>
+        <v>3.450580103383976</v>
       </c>
       <c r="E10" t="n">
-        <v>2.474137200697967</v>
+        <v>3.223128533645195</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>1.52507530283558</v>
       </c>
       <c r="E11" t="n">
-        <v>1.415558834122241</v>
+        <v>0.8188199201356429</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="H11" t="n">
-        <v>392</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12">
@@ -993,7 +993,7 @@
         <v>4.34388596682669</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>4.352399699368076</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7779198661937916</v>
+        <v>0.6979782637194548</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>2.335369605679624</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9951700386403913</v>
+        <v>0.7531235055540971</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1334</v>
+        <v>1376</v>
       </c>
       <c r="H17" t="n">
-        <v>1334</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="18">
@@ -1113,7 +1113,7 @@
         <v>7.382968998402578</v>
       </c>
       <c r="E18" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>3.296454899278627</v>
       </c>
       <c r="E19" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>52.2282354545503</v>
       </c>
       <c r="E21" t="n">
-        <v>9.640717166494472</v>
+        <v>10.1728501816377</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I320"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,7 +1972,7 @@
         <v>2.657422494291466</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9893952372926909</v>
+        <v>0.8927311657534539</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>2.657422494291466</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9893952372926909</v>
+        <v>0.8927311657534539</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>2.503316081052728</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9893952372926909</v>
+        <v>0.8927311657534539</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>2.284770260423371</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9893952372926909</v>
+        <v>0.8927311657534539</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1450</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="20">
@@ -3193,7 +3193,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G53" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G54" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>5.511564650052159</v>
       </c>
       <c r="G55" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>2.502521316381479</v>
       </c>
       <c r="G56" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>2.494773042596737</v>
       </c>
       <c r="G57" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58">
@@ -3358,7 +3358,7 @@
         <v>2.716787407556423</v>
       </c>
       <c r="G58" t="n">
-        <v>1.719020876401431</v>
+        <v>1.571556573867646</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>2.519746559167907</v>
       </c>
       <c r="G59" t="n">
-        <v>1.719020876401431</v>
+        <v>1.571556573867646</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>2.490677034056313</v>
       </c>
       <c r="G60" t="n">
-        <v>1.719020876401431</v>
+        <v>1.571556573867646</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1674</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="61">
@@ -3457,7 +3457,7 @@
         <v>2.688139529918372</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.5698075261183925</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>2.688139529918372</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.5698075261183925</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>2.688139529918372</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.5698075261183925</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>2.688139529918372</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.5698075261183925</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3589,15 +3589,15 @@
         <v>1.576958898590067</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.5698075261183925</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>112</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="66">
@@ -3655,7 +3655,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G69" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G71" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>3.722197753284193</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>2.059142234181705</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5631374833732654</v>
+        <v>0.5434627609743097</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>662</v>
+        <v>704</v>
       </c>
     </row>
     <row r="76">
@@ -3949,18 +3949,18 @@
         <v>0.6678972010595881</v>
       </c>
       <c r="F76" t="n">
-        <v>2.474137200697967</v>
+        <v>3.450580103383976</v>
       </c>
       <c r="G76" t="n">
-        <v>2.474137200697967</v>
+        <v>3.223128533645195</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
@@ -4069,22 +4069,22 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>44292</v>
+        <v>44536</v>
       </c>
       <c r="C80" t="n">
-        <v>100</v>
+        <v>2.751384371796668</v>
       </c>
       <c r="D80" t="n">
-        <v>1.207955082857578</v>
+        <v>2.465731574632679</v>
       </c>
       <c r="E80" t="n">
-        <v>98.79204491714242</v>
+        <v>0.2856527971639888</v>
       </c>
       <c r="F80" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G80" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -4102,22 +4102,22 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>44536</v>
+        <v>44545</v>
       </c>
       <c r="C81" t="n">
-        <v>100</v>
+        <v>2.751384371796668</v>
       </c>
       <c r="D81" t="n">
-        <v>2.465731574632679</v>
+        <v>2.483274816313459</v>
       </c>
       <c r="E81" t="n">
-        <v>97.53426842536732</v>
+        <v>0.2681095554832087</v>
       </c>
       <c r="F81" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G81" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4135,22 +4135,22 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>44545</v>
+        <v>44547</v>
       </c>
       <c r="C82" t="n">
-        <v>100</v>
+        <v>2.751384371796668</v>
       </c>
       <c r="D82" t="n">
-        <v>2.483274816313459</v>
+        <v>2.453747814427359</v>
       </c>
       <c r="E82" t="n">
-        <v>97.51672518368655</v>
+        <v>0.2976365573693087</v>
       </c>
       <c r="F82" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G82" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -4168,22 +4168,22 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>44547</v>
+        <v>44741</v>
       </c>
       <c r="C83" t="n">
-        <v>100</v>
+        <v>4.096306964887185</v>
       </c>
       <c r="D83" t="n">
-        <v>2.453747814427359</v>
+        <v>2.045911261975866</v>
       </c>
       <c r="E83" t="n">
-        <v>97.54625218557264</v>
+        <v>2.050395702911319</v>
       </c>
       <c r="F83" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G83" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -4201,22 +4201,22 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>44741</v>
+        <v>45775</v>
       </c>
       <c r="C84" t="n">
-        <v>100</v>
+        <v>8.032132497172121</v>
       </c>
       <c r="D84" t="n">
-        <v>2.045911261975866</v>
+        <v>2.436747151683569</v>
       </c>
       <c r="E84" t="n">
-        <v>97.95408873802414</v>
+        <v>5.595385345488552</v>
       </c>
       <c r="F84" t="n">
-        <v>8.032132497172121</v>
+        <v>2.522451549818021</v>
       </c>
       <c r="G84" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
@@ -4234,63 +4234,63 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45775</v>
+        <v>45791</v>
       </c>
       <c r="C85" t="n">
-        <v>100</v>
+        <v>8.032132497172121</v>
       </c>
       <c r="D85" t="n">
-        <v>2.436747151683569</v>
+        <v>2.389888398424347</v>
       </c>
       <c r="E85" t="n">
-        <v>97.56325284831644</v>
+        <v>5.642244098747774</v>
       </c>
       <c r="F85" t="n">
-        <v>2.522451549818021</v>
+        <v>2.407820094599427</v>
       </c>
       <c r="G85" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>14</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DKNG US Equity</t>
+          <t>DOCU US Equity</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45791</v>
+        <v>44209</v>
       </c>
       <c r="C86" t="n">
-        <v>100</v>
+        <v>2.564375265017821</v>
       </c>
       <c r="D86" t="n">
-        <v>2.389888398424347</v>
+        <v>2.484838642551234</v>
       </c>
       <c r="E86" t="n">
-        <v>97.61011160157565</v>
+        <v>0.07953662246658721</v>
       </c>
       <c r="F86" t="n">
-        <v>2.407820094599427</v>
+        <v>2.831192012453475</v>
       </c>
       <c r="G86" t="n">
-        <v>2.198252955153464</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>107</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87">
@@ -4300,19 +4300,19 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>44209</v>
+        <v>44452</v>
       </c>
       <c r="C87" t="n">
-        <v>2.564375265017821</v>
+        <v>2.831192012453475</v>
       </c>
       <c r="D87" t="n">
-        <v>2.484838642551234</v>
+        <v>2.473937736798025</v>
       </c>
       <c r="E87" t="n">
-        <v>0.07953662246658721</v>
+        <v>0.3572542756554502</v>
       </c>
       <c r="F87" t="n">
-        <v>2.831192012453475</v>
+        <v>2.522327498765969</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4333,16 +4333,16 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>44452</v>
+        <v>44456</v>
       </c>
       <c r="C88" t="n">
         <v>2.831192012453475</v>
       </c>
       <c r="D88" t="n">
-        <v>2.473937736798025</v>
+        <v>2.492475168420296</v>
       </c>
       <c r="E88" t="n">
-        <v>0.3572542756554502</v>
+        <v>0.3387168440331791</v>
       </c>
       <c r="F88" t="n">
         <v>2.522327498765969</v>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -4366,63 +4366,63 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>44456</v>
+        <v>44460</v>
       </c>
       <c r="C89" t="n">
         <v>2.831192012453475</v>
       </c>
       <c r="D89" t="n">
-        <v>2.492475168420296</v>
+        <v>2.36661532191609</v>
       </c>
       <c r="E89" t="n">
-        <v>0.3387168440331791</v>
+        <v>0.4645766905373852</v>
       </c>
       <c r="F89" t="n">
-        <v>2.522327498765969</v>
+        <v>2.471763982420601</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DOCU US Equity</t>
+          <t>DSY SJ Equity</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>44460</v>
+        <v>44561</v>
       </c>
       <c r="C90" t="n">
-        <v>2.831192012453475</v>
+        <v>2.514523757317722</v>
       </c>
       <c r="D90" t="n">
-        <v>2.36661532191609</v>
+        <v>2.487535116093207</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4645766905373852</v>
+        <v>0.02698864122451505</v>
       </c>
       <c r="F90" t="n">
-        <v>2.471763982420601</v>
+        <v>6.174456053035262</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>181</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -4432,22 +4432,22 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>44561</v>
+        <v>45271</v>
       </c>
       <c r="C91" t="n">
-        <v>2.514523757317722</v>
+        <v>6.174456053035262</v>
       </c>
       <c r="D91" t="n">
-        <v>2.487535116093207</v>
+        <v>2.47420573482181</v>
       </c>
       <c r="E91" t="n">
-        <v>0.02698864122451505</v>
+        <v>3.700250318213452</v>
       </c>
       <c r="F91" t="n">
-        <v>6.174456053035262</v>
+        <v>2.679612299614464</v>
       </c>
       <c r="G91" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4465,22 +4465,22 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45271</v>
+        <v>45274</v>
       </c>
       <c r="C92" t="n">
         <v>6.174456053035262</v>
       </c>
       <c r="D92" t="n">
-        <v>2.47420573482181</v>
+        <v>2.492666041315427</v>
       </c>
       <c r="E92" t="n">
-        <v>3.700250318213452</v>
+        <v>3.681790011719835</v>
       </c>
       <c r="F92" t="n">
         <v>2.679612299614464</v>
       </c>
       <c r="G92" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4498,22 +4498,22 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45274</v>
+        <v>45279</v>
       </c>
       <c r="C93" t="n">
         <v>6.174456053035262</v>
       </c>
       <c r="D93" t="n">
-        <v>2.492666041315427</v>
+        <v>2.45138105978905</v>
       </c>
       <c r="E93" t="n">
-        <v>3.681790011719835</v>
+        <v>3.723074993246211</v>
       </c>
       <c r="F93" t="n">
         <v>2.679612299614464</v>
       </c>
       <c r="G93" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
@@ -4531,22 +4531,22 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45279</v>
+        <v>45301</v>
       </c>
       <c r="C94" t="n">
         <v>6.174456053035262</v>
       </c>
       <c r="D94" t="n">
-        <v>2.45138105978905</v>
+        <v>2.484700060356837</v>
       </c>
       <c r="E94" t="n">
-        <v>3.723074993246211</v>
+        <v>3.689755992678425</v>
       </c>
       <c r="F94" t="n">
         <v>2.679612299614464</v>
       </c>
       <c r="G94" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4564,22 +4564,22 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45301</v>
+        <v>45308</v>
       </c>
       <c r="C95" t="n">
         <v>6.174456053035262</v>
       </c>
       <c r="D95" t="n">
-        <v>2.484700060356837</v>
+        <v>2.446226906301442</v>
       </c>
       <c r="E95" t="n">
-        <v>3.689755992678425</v>
+        <v>3.72822914673382</v>
       </c>
       <c r="F95" t="n">
         <v>2.679612299614464</v>
       </c>
       <c r="G95" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -4597,22 +4597,22 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45308</v>
+        <v>45327</v>
       </c>
       <c r="C96" t="n">
         <v>6.174456053035262</v>
       </c>
       <c r="D96" t="n">
-        <v>2.446226906301442</v>
+        <v>2.414006403378029</v>
       </c>
       <c r="E96" t="n">
-        <v>3.72822914673382</v>
+        <v>3.760449649657233</v>
       </c>
       <c r="F96" t="n">
         <v>2.679612299614464</v>
       </c>
       <c r="G96" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>15</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97">
@@ -4630,63 +4630,63 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45327</v>
+        <v>45511</v>
       </c>
       <c r="C97" t="n">
         <v>6.174456053035262</v>
       </c>
       <c r="D97" t="n">
-        <v>2.414006403378029</v>
+        <v>2.43323302163862</v>
       </c>
       <c r="E97" t="n">
-        <v>3.760449649657233</v>
+        <v>3.741223031396641</v>
       </c>
       <c r="F97" t="n">
-        <v>2.679612299614464</v>
+        <v>2.43323302163862</v>
       </c>
       <c r="G97" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>178</v>
+        <v>429</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DSY SJ Equity</t>
+          <t>ETSY US Equity</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45511</v>
+        <v>44509</v>
       </c>
       <c r="C98" t="n">
-        <v>6.174456053035262</v>
+        <v>2.610021536297876</v>
       </c>
       <c r="D98" t="n">
-        <v>2.43323302163862</v>
+        <v>2.496882054364851</v>
       </c>
       <c r="E98" t="n">
-        <v>3.741223031396641</v>
+        <v>0.1131394819330249</v>
       </c>
       <c r="F98" t="n">
-        <v>2.43323302163862</v>
+        <v>3.184008808807393</v>
       </c>
       <c r="G98" t="n">
-        <v>1.105259630764662</v>
+        <v>0</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>387</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4696,19 +4696,19 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>44509</v>
+        <v>44574</v>
       </c>
       <c r="C99" t="n">
-        <v>2.610021536297876</v>
+        <v>3.184008808807393</v>
       </c>
       <c r="D99" t="n">
-        <v>2.496882054364851</v>
+        <v>2.453380327906987</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1131394819330249</v>
+        <v>0.7306284809004064</v>
       </c>
       <c r="F99" t="n">
-        <v>3.184008808807393</v>
+        <v>2.55064920991502</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
@@ -4729,16 +4729,16 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>44574</v>
+        <v>44582</v>
       </c>
       <c r="C100" t="n">
         <v>3.184008808807393</v>
       </c>
       <c r="D100" t="n">
-        <v>2.453380327906987</v>
+        <v>2.483371482879665</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7306284809004064</v>
+        <v>0.7006373259277283</v>
       </c>
       <c r="F100" t="n">
         <v>2.55064920991502</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -4762,19 +4762,19 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>44582</v>
+        <v>44587</v>
       </c>
       <c r="C101" t="n">
         <v>3.184008808807393</v>
       </c>
       <c r="D101" t="n">
-        <v>2.483371482879665</v>
+        <v>2.462557419409553</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7006373259277283</v>
+        <v>0.7214513893978407</v>
       </c>
       <c r="F101" t="n">
-        <v>2.55064920991502</v>
+        <v>2.519925637621451</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -4795,63 +4795,63 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>44587</v>
+        <v>44593</v>
       </c>
       <c r="C102" t="n">
         <v>3.184008808807393</v>
       </c>
       <c r="D102" t="n">
-        <v>2.462557419409553</v>
+        <v>2.018942548846722</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7214513893978407</v>
+        <v>1.165066259960672</v>
       </c>
       <c r="F102" t="n">
-        <v>2.519925637621451</v>
+        <v>2.018942548846722</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>143</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ETSY US Equity</t>
+          <t>FTOXX US Equity</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>44593</v>
+        <v>45918</v>
       </c>
       <c r="C103" t="n">
-        <v>3.184008808807393</v>
+        <v>5.18211727045122</v>
       </c>
       <c r="D103" t="n">
-        <v>2.018942548846722</v>
+        <v>1.87691424329679</v>
       </c>
       <c r="E103" t="n">
-        <v>1.165066259960672</v>
+        <v>3.305203027154429</v>
       </c>
       <c r="F103" t="n">
-        <v>2.018942548846722</v>
+        <v>1.87691424329679</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.1914413833558123</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>143</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -4876,7 +4876,7 @@
         <v>5.064178137113904</v>
       </c>
       <c r="G104" t="n">
-        <v>0.9980327726384945</v>
+        <v>0.9447343673179117</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>2.35343865246932</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9980327726384945</v>
+        <v>0.9447343673179117</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>477</v>
+        <v>519</v>
       </c>
     </row>
     <row r="106">
@@ -5173,7 +5173,7 @@
         <v>4.34388596682669</v>
       </c>
       <c r="G113" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>4.34388596682669</v>
       </c>
       <c r="G114" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>4.34388596682669</v>
       </c>
       <c r="G115" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>4.34388596682669</v>
       </c>
       <c r="G116" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>4.34388596682669</v>
       </c>
       <c r="G117" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>4.34388596682669</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>2.45212371382027</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7599830967000712</v>
+        <v>0.6354229613580908</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1577</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="120">
@@ -5404,7 +5404,7 @@
         <v>4.352399699368076</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7779198661937916</v>
+        <v>0.6979782637194548</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>2.412627967290023</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7779198661937916</v>
+        <v>0.6979782637194548</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>388</v>
+        <v>430</v>
       </c>
     </row>
     <row r="122">
@@ -6196,7 +6196,7 @@
         <v>7.382968998402578</v>
       </c>
       <c r="G144" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>7.382968998402578</v>
       </c>
       <c r="G145" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>7.382968998402578</v>
       </c>
       <c r="G146" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>4.049614667826542</v>
       </c>
       <c r="G147" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6309,26 +6309,26 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>META US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>44264</v>
+        <v>45932</v>
       </c>
       <c r="C148" t="n">
-        <v>2.880472914307394</v>
+        <v>7.382968998402578</v>
       </c>
       <c r="D148" t="n">
-        <v>2.209129042755991</v>
+        <v>2.395942264594711</v>
       </c>
       <c r="E148" t="n">
-        <v>0.6713438715514028</v>
+        <v>4.987026733807868</v>
       </c>
       <c r="F148" t="n">
-        <v>3.296454899278627</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="G148" t="n">
-        <v>2.262043393998077</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
@@ -6346,22 +6346,22 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>44327</v>
+        <v>44264</v>
       </c>
       <c r="C149" t="n">
         <v>2.880472914307394</v>
       </c>
       <c r="D149" t="n">
-        <v>2.496064257248813</v>
+        <v>2.209129042755991</v>
       </c>
       <c r="E149" t="n">
-        <v>0.384408657058581</v>
+        <v>0.6713438715514028</v>
       </c>
       <c r="F149" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="G149" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="150">
@@ -6379,22 +6379,22 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>44365</v>
+        <v>44327</v>
       </c>
       <c r="C150" t="n">
         <v>2.880472914307394</v>
       </c>
       <c r="D150" t="n">
-        <v>2.468319742043182</v>
+        <v>2.496064257248813</v>
       </c>
       <c r="E150" t="n">
-        <v>0.4121531722642122</v>
+        <v>0.384408657058581</v>
       </c>
       <c r="F150" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="G150" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>44371</v>
+        <v>44365</v>
       </c>
       <c r="C151" t="n">
         <v>2.880472914307394</v>
       </c>
       <c r="D151" t="n">
-        <v>2.471950817247284</v>
+        <v>2.468319742043182</v>
       </c>
       <c r="E151" t="n">
-        <v>0.4085220970601102</v>
+        <v>0.4121531722642122</v>
       </c>
       <c r="F151" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="G151" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>44453</v>
+        <v>44371</v>
       </c>
       <c r="C152" t="n">
         <v>2.880472914307394</v>
       </c>
       <c r="D152" t="n">
-        <v>2.318618569374694</v>
+        <v>2.471950817247284</v>
       </c>
       <c r="E152" t="n">
-        <v>0.5618543449327</v>
+        <v>0.4085220970601102</v>
       </c>
       <c r="F152" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="G152" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
@@ -6478,22 +6478,22 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>44523</v>
+        <v>44453</v>
       </c>
       <c r="C153" t="n">
+        <v>2.880472914307394</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.318618569374694</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.5618543449327</v>
+      </c>
+      <c r="F153" t="n">
         <v>3.296454899278627</v>
       </c>
-      <c r="D153" t="n">
-        <v>1.617776507282425</v>
-      </c>
-      <c r="E153" t="n">
-        <v>1.678678391996202</v>
-      </c>
-      <c r="F153" t="n">
-        <v>3.055749512656296</v>
-      </c>
       <c r="G153" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>958</v>
+        <v>52</v>
       </c>
     </row>
     <row r="154">
@@ -6511,22 +6511,22 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>45485</v>
+        <v>44523</v>
       </c>
       <c r="C154" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D154" t="n">
-        <v>2.465157261401766</v>
+        <v>1.617776507282425</v>
       </c>
       <c r="E154" t="n">
-        <v>0.8312976378768613</v>
+        <v>1.678678391996202</v>
       </c>
       <c r="F154" t="n">
         <v>3.055749512656296</v>
       </c>
       <c r="G154" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>21</v>
+        <v>958</v>
       </c>
     </row>
     <row r="155">
@@ -6544,22 +6544,22 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>45614</v>
+        <v>45485</v>
       </c>
       <c r="C155" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D155" t="n">
-        <v>2.439539650844424</v>
+        <v>2.465157261401766</v>
       </c>
       <c r="E155" t="n">
-        <v>0.8569152484342033</v>
+        <v>0.8312976378768613</v>
       </c>
       <c r="F155" t="n">
-        <v>2.940963121504008</v>
+        <v>3.055749512656296</v>
       </c>
       <c r="G155" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156">
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>45631</v>
+        <v>45614</v>
       </c>
       <c r="C156" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D156" t="n">
-        <v>2.453617861364709</v>
+        <v>2.439539650844424</v>
       </c>
       <c r="E156" t="n">
-        <v>0.8428370379139185</v>
+        <v>0.8569152484342033</v>
       </c>
       <c r="F156" t="n">
         <v>2.940963121504008</v>
       </c>
       <c r="G156" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157">
@@ -6610,22 +6610,22 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45643</v>
+        <v>45631</v>
       </c>
       <c r="C157" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D157" t="n">
-        <v>2.487692015210635</v>
+        <v>2.453617861364709</v>
       </c>
       <c r="E157" t="n">
-        <v>0.8087628840679923</v>
+        <v>0.8428370379139185</v>
       </c>
       <c r="F157" t="n">
         <v>2.940963121504008</v>
       </c>
       <c r="G157" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
@@ -6643,22 +6643,22 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>45649</v>
+        <v>45643</v>
       </c>
       <c r="C158" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D158" t="n">
-        <v>2.46897847834334</v>
+        <v>2.487692015210635</v>
       </c>
       <c r="E158" t="n">
-        <v>0.8274764209352874</v>
+        <v>0.8087628840679923</v>
       </c>
       <c r="F158" t="n">
         <v>2.940963121504008</v>
       </c>
       <c r="G158" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>45679</v>
+        <v>45649</v>
       </c>
       <c r="C159" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D159" t="n">
-        <v>2.480655088785714</v>
+        <v>2.46897847834334</v>
       </c>
       <c r="E159" t="n">
-        <v>0.8157998104929134</v>
+        <v>0.8274764209352874</v>
       </c>
       <c r="F159" t="n">
         <v>2.940963121504008</v>
       </c>
       <c r="G159" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6709,22 +6709,22 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45769</v>
+        <v>45679</v>
       </c>
       <c r="C160" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D160" t="n">
-        <v>2.466345757424845</v>
+        <v>2.480655088785714</v>
       </c>
       <c r="E160" t="n">
-        <v>0.8301091418537823</v>
+        <v>0.8157998104929134</v>
       </c>
       <c r="F160" t="n">
-        <v>2.812501256286416</v>
+        <v>2.940963121504008</v>
       </c>
       <c r="G160" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -6742,22 +6742,22 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>45825</v>
+        <v>45769</v>
       </c>
       <c r="C161" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D161" t="n">
-        <v>2.485825564558603</v>
+        <v>2.466345757424845</v>
       </c>
       <c r="E161" t="n">
-        <v>0.8106293347200246</v>
+        <v>0.8301091418537823</v>
       </c>
       <c r="F161" t="n">
-        <v>2.505033647041904</v>
+        <v>2.812501256286416</v>
       </c>
       <c r="G161" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
@@ -6775,63 +6775,63 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>45828</v>
+        <v>45825</v>
       </c>
       <c r="C162" t="n">
         <v>3.296454899278627</v>
       </c>
       <c r="D162" t="n">
-        <v>2.411872396845016</v>
+        <v>2.485825564558603</v>
       </c>
       <c r="E162" t="n">
-        <v>0.8845825024336116</v>
+        <v>0.8106293347200246</v>
       </c>
       <c r="F162" t="n">
-        <v>2.428275925010792</v>
+        <v>2.505033647041904</v>
       </c>
       <c r="G162" t="n">
-        <v>2.262043393998077</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NU US Equity</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45233</v>
+        <v>45828</v>
       </c>
       <c r="C163" t="n">
-        <v>2.578322759398403</v>
+        <v>3.296454899278627</v>
       </c>
       <c r="D163" t="n">
-        <v>2.376805970842833</v>
+        <v>2.411872396845016</v>
       </c>
       <c r="E163" t="n">
-        <v>0.20151678855557</v>
+        <v>0.8845825024336116</v>
       </c>
       <c r="F163" t="n">
-        <v>2.840734657079368</v>
+        <v>2.428275925010792</v>
       </c>
       <c r="G163" t="n">
-        <v>1.569216533760492</v>
+        <v>2.053738889935192</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="164">
@@ -6841,63 +6841,63 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>45401</v>
+        <v>45233</v>
       </c>
       <c r="C164" t="n">
+        <v>2.578322759398403</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2.376805970842833</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.20151678855557</v>
+      </c>
+      <c r="F164" t="n">
         <v>2.840734657079368</v>
       </c>
-      <c r="D164" t="n">
-        <v>1.951850593504946</v>
-      </c>
-      <c r="E164" t="n">
-        <v>0.8888840635744222</v>
-      </c>
-      <c r="F164" t="n">
-        <v>2.330350639762174</v>
-      </c>
       <c r="G164" t="n">
-        <v>1.569216533760492</v>
+        <v>1.518222353184329</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>497</v>
+        <v>131</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NVDA US Equity</t>
+          <t>NU US Equity</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>43598</v>
+        <v>45401</v>
       </c>
       <c r="C165" t="n">
-        <v>3.7496787649484</v>
+        <v>2.840734657079368</v>
       </c>
       <c r="D165" t="n">
-        <v>2.465131415441042</v>
+        <v>1.951850593504946</v>
       </c>
       <c r="E165" t="n">
-        <v>1.284547349507358</v>
+        <v>0.8888840635744222</v>
       </c>
       <c r="F165" t="n">
-        <v>3.142139441352972</v>
+        <v>2.330350639762174</v>
       </c>
       <c r="G165" t="n">
-        <v>1.287732591107519</v>
+        <v>1.518222353184329</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3</v>
+        <v>539</v>
       </c>
     </row>
     <row r="166">
@@ -6907,22 +6907,22 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>43605</v>
+        <v>43598</v>
       </c>
       <c r="C166" t="n">
         <v>3.7496787649484</v>
       </c>
       <c r="D166" t="n">
-        <v>2.487053786663195</v>
+        <v>2.465131415441042</v>
       </c>
       <c r="E166" t="n">
-        <v>1.262624978285205</v>
+        <v>1.284547349507358</v>
       </c>
       <c r="F166" t="n">
         <v>3.142139441352972</v>
       </c>
       <c r="G166" t="n">
-        <v>1.287732591107519</v>
+        <v>1.279638415514854</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>43607</v>
+        <v>43605</v>
       </c>
       <c r="C167" t="n">
         <v>3.7496787649484</v>
       </c>
       <c r="D167" t="n">
-        <v>2.471780659347769</v>
+        <v>2.487053786663195</v>
       </c>
       <c r="E167" t="n">
-        <v>1.277898105600631</v>
+        <v>1.262624978285205</v>
       </c>
       <c r="F167" t="n">
         <v>3.142139441352972</v>
       </c>
       <c r="G167" t="n">
-        <v>1.287732591107519</v>
+        <v>1.279638415514854</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -6973,63 +6973,63 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>43712</v>
+        <v>43607</v>
       </c>
       <c r="C168" t="n">
         <v>3.7496787649484</v>
       </c>
       <c r="D168" t="n">
-        <v>2.074707295034011</v>
+        <v>2.471780659347769</v>
       </c>
       <c r="E168" t="n">
-        <v>1.674971469914389</v>
+        <v>1.277898105600631</v>
       </c>
       <c r="F168" t="n">
-        <v>2.468445570641949</v>
+        <v>3.142139441352972</v>
       </c>
       <c r="G168" t="n">
-        <v>1.287732591107519</v>
+        <v>1.279638415514854</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2186</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OPEN US Equity</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>44260</v>
+        <v>43712</v>
       </c>
       <c r="C169" t="n">
-        <v>3.00875036127864</v>
+        <v>3.7496787649484</v>
       </c>
       <c r="D169" t="n">
-        <v>2.356210034962092</v>
+        <v>2.074707295034011</v>
       </c>
       <c r="E169" t="n">
-        <v>0.6525403263165477</v>
+        <v>1.674971469914389</v>
       </c>
       <c r="F169" t="n">
-        <v>3.723682921551021</v>
+        <v>2.468445570641949</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>1.279638415514854</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="170">
@@ -7039,16 +7039,16 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>44279</v>
+        <v>44260</v>
       </c>
       <c r="C170" t="n">
         <v>3.00875036127864</v>
       </c>
       <c r="D170" t="n">
-        <v>2.474011401857643</v>
+        <v>2.356210034962092</v>
       </c>
       <c r="E170" t="n">
-        <v>0.5347389594209968</v>
+        <v>0.6525403263165477</v>
       </c>
       <c r="F170" t="n">
         <v>3.723682921551021</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
@@ -7072,16 +7072,16 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>44302</v>
+        <v>44279</v>
       </c>
       <c r="C171" t="n">
         <v>3.00875036127864</v>
       </c>
       <c r="D171" t="n">
-        <v>2.361900772405058</v>
+        <v>2.474011401857643</v>
       </c>
       <c r="E171" t="n">
-        <v>0.6468495888735819</v>
+        <v>0.5347389594209968</v>
       </c>
       <c r="F171" t="n">
         <v>3.723682921551021</v>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -7105,16 +7105,16 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>44329</v>
+        <v>44292</v>
       </c>
       <c r="C172" t="n">
-        <v>3.107271699198208</v>
+        <v>3.00875036127864</v>
       </c>
       <c r="D172" t="n">
-        <v>2.402443222457289</v>
+        <v>2.471605896267512</v>
       </c>
       <c r="E172" t="n">
-        <v>0.7048284767409192</v>
+        <v>0.5371444650111279</v>
       </c>
       <c r="F172" t="n">
         <v>3.723682921551021</v>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -7138,16 +7138,16 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>44335</v>
+        <v>44302</v>
       </c>
       <c r="C173" t="n">
-        <v>3.107271699198208</v>
+        <v>3.00875036127864</v>
       </c>
       <c r="D173" t="n">
-        <v>2.401301443252714</v>
+        <v>2.361900772405058</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7059702559454943</v>
+        <v>0.6468495888735819</v>
       </c>
       <c r="F173" t="n">
         <v>3.723682921551021</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
@@ -7171,16 +7171,16 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>44362</v>
+        <v>44329</v>
       </c>
       <c r="C174" t="n">
         <v>3.107271699198208</v>
       </c>
       <c r="D174" t="n">
-        <v>2.478457796731573</v>
+        <v>2.402443222457289</v>
       </c>
       <c r="E174" t="n">
-        <v>0.6288139024666353</v>
+        <v>0.7048284767409192</v>
       </c>
       <c r="F174" t="n">
         <v>3.723682921551021</v>
@@ -7204,16 +7204,16 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>44364</v>
+        <v>44335</v>
       </c>
       <c r="C175" t="n">
         <v>3.107271699198208</v>
       </c>
       <c r="D175" t="n">
-        <v>2.48403751240901</v>
+        <v>2.401301443252714</v>
       </c>
       <c r="E175" t="n">
-        <v>0.623234186789198</v>
+        <v>0.7059702559454943</v>
       </c>
       <c r="F175" t="n">
         <v>3.723682921551021</v>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176">
@@ -7237,16 +7237,16 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>44376</v>
+        <v>44362</v>
       </c>
       <c r="C176" t="n">
         <v>3.107271699198208</v>
       </c>
       <c r="D176" t="n">
-        <v>2.429105612980547</v>
+        <v>2.478457796731573</v>
       </c>
       <c r="E176" t="n">
-        <v>0.6781660862176611</v>
+        <v>0.6288139024666353</v>
       </c>
       <c r="F176" t="n">
         <v>3.723682921551021</v>
@@ -7270,16 +7270,16 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>44378</v>
+        <v>44364</v>
       </c>
       <c r="C177" t="n">
         <v>3.107271699198208</v>
       </c>
       <c r="D177" t="n">
-        <v>2.444486651411696</v>
+        <v>2.48403751240901</v>
       </c>
       <c r="E177" t="n">
-        <v>0.662785047786512</v>
+        <v>0.623234186789198</v>
       </c>
       <c r="F177" t="n">
         <v>3.723682921551021</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178">
@@ -7303,20 +7303,20 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>44508</v>
+        <v>44376</v>
       </c>
       <c r="C178" t="n">
+        <v>3.107271699198208</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2.429105612980547</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.6781660862176611</v>
+      </c>
+      <c r="F178" t="n">
         <v>3.723682921551021</v>
       </c>
-      <c r="D178" t="n">
-        <v>2.382923724522589</v>
-      </c>
-      <c r="E178" t="n">
-        <v>1.340759197028432</v>
-      </c>
-      <c r="F178" t="n">
-        <v>2.503231438826591</v>
-      </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -7336,52 +7336,52 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>44516</v>
+        <v>44378</v>
       </c>
       <c r="C179" t="n">
+        <v>3.107271699198208</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2.444486651411696</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.662785047786512</v>
+      </c>
+      <c r="F179" t="n">
         <v>3.723682921551021</v>
       </c>
-      <c r="D179" t="n">
-        <v>2.062222539272248</v>
-      </c>
-      <c r="E179" t="n">
-        <v>1.661460382278773</v>
-      </c>
-      <c r="F179" t="n">
-        <v>2.062222539272248</v>
-      </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>112</v>
+        <v>27</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PATH US Equity</t>
+          <t>OPEN US Equity</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>44410</v>
+        <v>44508</v>
       </c>
       <c r="C180" t="n">
-        <v>2.559600137546801</v>
+        <v>3.723682921551021</v>
       </c>
       <c r="D180" t="n">
-        <v>2.401249787564858</v>
+        <v>2.382923724522589</v>
       </c>
       <c r="E180" t="n">
-        <v>0.1583503499819434</v>
+        <v>1.340759197028432</v>
       </c>
       <c r="F180" t="n">
-        <v>7.714164468316685</v>
+        <v>2.503231438826591</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -7392,40 +7392,40 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PATH US Equity</t>
+          <t>OPEN US Equity</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>44414</v>
+        <v>44516</v>
       </c>
       <c r="C181" t="n">
-        <v>2.559600137546801</v>
+        <v>3.723682921551021</v>
       </c>
       <c r="D181" t="n">
-        <v>2.488619536905342</v>
+        <v>2.062222539272248</v>
       </c>
       <c r="E181" t="n">
-        <v>0.07098060064145928</v>
+        <v>1.661460382278773</v>
       </c>
       <c r="F181" t="n">
-        <v>7.714164468316685</v>
+        <v>2.062222539272248</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
     </row>
     <row r="182">
@@ -7435,16 +7435,16 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>44420</v>
+        <v>44410</v>
       </c>
       <c r="C182" t="n">
         <v>2.559600137546801</v>
       </c>
       <c r="D182" t="n">
-        <v>2.445274326856459</v>
+        <v>2.401249787564858</v>
       </c>
       <c r="E182" t="n">
-        <v>0.114325810690342</v>
+        <v>0.1583503499819434</v>
       </c>
       <c r="F182" t="n">
         <v>7.714164468316685</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -7468,16 +7468,16 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>44448</v>
+        <v>44414</v>
       </c>
       <c r="C183" t="n">
-        <v>2.899709586704036</v>
+        <v>2.559600137546801</v>
       </c>
       <c r="D183" t="n">
-        <v>2.438818385674557</v>
+        <v>2.488619536905342</v>
       </c>
       <c r="E183" t="n">
-        <v>0.460891201029479</v>
+        <v>0.07098060064145928</v>
       </c>
       <c r="F183" t="n">
         <v>7.714164468316685</v>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -7501,16 +7501,16 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>44454</v>
+        <v>44420</v>
       </c>
       <c r="C184" t="n">
-        <v>2.899709586704036</v>
+        <v>2.559600137546801</v>
       </c>
       <c r="D184" t="n">
-        <v>2.459447547356414</v>
+        <v>2.445274326856459</v>
       </c>
       <c r="E184" t="n">
-        <v>0.4402620393476222</v>
+        <v>0.114325810690342</v>
       </c>
       <c r="F184" t="n">
         <v>7.714164468316685</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
@@ -7534,20 +7534,20 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>45589</v>
+        <v>44448</v>
       </c>
       <c r="C185" t="n">
+        <v>2.899709586704036</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2.438818385674557</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.460891201029479</v>
+      </c>
+      <c r="F185" t="n">
         <v>7.714164468316685</v>
       </c>
-      <c r="D185" t="n">
-        <v>2.43898881553762</v>
-      </c>
-      <c r="E185" t="n">
-        <v>5.275175652779065</v>
-      </c>
-      <c r="F185" t="n">
-        <v>2.653169874311598</v>
-      </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -7567,20 +7567,20 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>45601</v>
+        <v>44454</v>
       </c>
       <c r="C186" t="n">
+        <v>2.899709586704036</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2.459447547356414</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.4402620393476222</v>
+      </c>
+      <c r="F186" t="n">
         <v>7.714164468316685</v>
       </c>
-      <c r="D186" t="n">
-        <v>2.488720624089018</v>
-      </c>
-      <c r="E186" t="n">
-        <v>5.225443844227668</v>
-      </c>
-      <c r="F186" t="n">
-        <v>2.653169874311598</v>
-      </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
@@ -7600,52 +7600,52 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>45607</v>
+        <v>45589</v>
       </c>
       <c r="C187" t="n">
         <v>7.714164468316685</v>
       </c>
       <c r="D187" t="n">
-        <v>2.358501798993907</v>
+        <v>2.43898881553762</v>
       </c>
       <c r="E187" t="n">
-        <v>5.355662669322778</v>
+        <v>5.275175652779065</v>
       </c>
       <c r="F187" t="n">
-        <v>2.406625105405453</v>
+        <v>2.653169874311598</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>192</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PDD US Equity</t>
+          <t>PATH US Equity</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>43789</v>
+        <v>45601</v>
       </c>
       <c r="C188" t="n">
-        <v>4.165412687322243</v>
+        <v>7.714164468316685</v>
       </c>
       <c r="D188" t="n">
-        <v>2.066106740269994</v>
+        <v>2.488720624089018</v>
       </c>
       <c r="E188" t="n">
-        <v>2.099305947052249</v>
+        <v>5.225443844227668</v>
       </c>
       <c r="F188" t="n">
-        <v>3.78477560521101</v>
+        <v>2.653169874311598</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -7656,40 +7656,40 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PDD US Equity</t>
+          <t>PATH US Equity</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>43839</v>
+        <v>45607</v>
       </c>
       <c r="C189" t="n">
-        <v>4.165412687322243</v>
+        <v>7.714164468316685</v>
       </c>
       <c r="D189" t="n">
-        <v>2.425615309505744</v>
+        <v>2.358501798993907</v>
       </c>
       <c r="E189" t="n">
-        <v>1.739797377816499</v>
+        <v>5.355662669322778</v>
       </c>
       <c r="F189" t="n">
-        <v>3.78477560521101</v>
+        <v>2.406625105405453</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>49</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190">
@@ -7699,16 +7699,16 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>43893</v>
+        <v>43789</v>
       </c>
       <c r="C190" t="n">
         <v>4.165412687322243</v>
       </c>
       <c r="D190" t="n">
-        <v>2.380626604182905</v>
+        <v>2.066106740269994</v>
       </c>
       <c r="E190" t="n">
-        <v>1.784786083139339</v>
+        <v>2.099305947052249</v>
       </c>
       <c r="F190" t="n">
         <v>3.78477560521101</v>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="191">
@@ -7732,55 +7732,55 @@
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>44027</v>
+        <v>43839</v>
       </c>
       <c r="C191" t="n">
         <v>4.165412687322243</v>
       </c>
       <c r="D191" t="n">
-        <v>1.149771294380487</v>
+        <v>2.425615309505744</v>
       </c>
       <c r="E191" t="n">
-        <v>3.015641392941756</v>
+        <v>1.739797377816499</v>
       </c>
       <c r="F191" t="n">
-        <v>2.466055064942712</v>
+        <v>3.78477560521101</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>566</v>
+        <v>49</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PINS US Equity</t>
+          <t>PDD US Equity</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>43865</v>
+        <v>43893</v>
       </c>
       <c r="C192" t="n">
-        <v>2.546729478339548</v>
+        <v>4.165412687322243</v>
       </c>
       <c r="D192" t="n">
-        <v>2.494718503144879</v>
+        <v>2.380626604182905</v>
       </c>
       <c r="E192" t="n">
-        <v>0.05201097519466868</v>
+        <v>1.784786083139339</v>
       </c>
       <c r="F192" t="n">
-        <v>5.928497681120896</v>
+        <v>3.78477560521101</v>
       </c>
       <c r="G192" t="n">
-        <v>2.298359534275684</v>
+        <v>0</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -7788,40 +7788,40 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PINS US Equity</t>
+          <t>PDD US Equity</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>43900</v>
+        <v>44027</v>
       </c>
       <c r="C193" t="n">
-        <v>2.89709242439212</v>
+        <v>4.165412687322243</v>
       </c>
       <c r="D193" t="n">
-        <v>2.48751834136162</v>
+        <v>1.149771294380487</v>
       </c>
       <c r="E193" t="n">
-        <v>0.4095740830305004</v>
+        <v>3.015641392941756</v>
       </c>
       <c r="F193" t="n">
-        <v>5.928497681120896</v>
+        <v>2.466055064942712</v>
       </c>
       <c r="G193" t="n">
-        <v>2.298359534275684</v>
+        <v>0</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>7</v>
+        <v>566</v>
       </c>
     </row>
     <row r="194">
@@ -7831,22 +7831,22 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>43908</v>
+        <v>43865</v>
       </c>
       <c r="C194" t="n">
-        <v>2.89709242439212</v>
+        <v>2.546729478339548</v>
       </c>
       <c r="D194" t="n">
-        <v>2.337238683156627</v>
+        <v>2.494718503144879</v>
       </c>
       <c r="E194" t="n">
-        <v>0.5598537412354934</v>
+        <v>0.05201097519466868</v>
       </c>
       <c r="F194" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="G194" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -7864,22 +7864,22 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>44446</v>
+        <v>43900</v>
       </c>
       <c r="C195" t="n">
+        <v>2.89709242439212</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.48751834136162</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.4095740830305004</v>
+      </c>
+      <c r="F195" t="n">
         <v>5.928497681120896</v>
       </c>
-      <c r="D195" t="n">
-        <v>2.477895369534514</v>
-      </c>
-      <c r="E195" t="n">
-        <v>3.450602311586382</v>
-      </c>
-      <c r="F195" t="n">
-        <v>4.350487315072731</v>
-      </c>
       <c r="G195" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -7897,22 +7897,22 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>44460</v>
+        <v>43908</v>
       </c>
       <c r="C196" t="n">
+        <v>2.89709242439212</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.337238683156627</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.5598537412354934</v>
+      </c>
+      <c r="F196" t="n">
         <v>5.928497681120896</v>
       </c>
-      <c r="D196" t="n">
-        <v>2.490187250580924</v>
-      </c>
-      <c r="E196" t="n">
-        <v>3.438310430539972</v>
-      </c>
-      <c r="F196" t="n">
-        <v>4.350487315072731</v>
-      </c>
       <c r="G196" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -7930,22 +7930,22 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>44474</v>
+        <v>44446</v>
       </c>
       <c r="C197" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D197" t="n">
-        <v>2.475019180263719</v>
+        <v>2.477895369534514</v>
       </c>
       <c r="E197" t="n">
-        <v>3.453478500857177</v>
+        <v>3.450602311586382</v>
       </c>
       <c r="F197" t="n">
         <v>4.350487315072731</v>
       </c>
       <c r="G197" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -7963,22 +7963,22 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>44495</v>
+        <v>44460</v>
       </c>
       <c r="C198" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D198" t="n">
-        <v>1.797032923960168</v>
+        <v>2.490187250580924</v>
       </c>
       <c r="E198" t="n">
-        <v>4.131464757160728</v>
+        <v>3.438310430539972</v>
       </c>
       <c r="F198" t="n">
         <v>4.350487315072731</v>
       </c>
       <c r="G198" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>840</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -7996,22 +7996,22 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>45342</v>
+        <v>44474</v>
       </c>
       <c r="C199" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D199" t="n">
-        <v>2.47832820120066</v>
+        <v>2.475019180263719</v>
       </c>
       <c r="E199" t="n">
-        <v>3.450169479920236</v>
+        <v>3.453478500857177</v>
       </c>
       <c r="F199" t="n">
         <v>4.350487315072731</v>
       </c>
       <c r="G199" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200">
@@ -8029,22 +8029,22 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>45355</v>
+        <v>44495</v>
       </c>
       <c r="C200" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D200" t="n">
-        <v>2.499070935848451</v>
+        <v>1.797032923960168</v>
       </c>
       <c r="E200" t="n">
-        <v>3.429426745272445</v>
+        <v>4.131464757160728</v>
       </c>
       <c r="F200" t="n">
         <v>4.350487315072731</v>
       </c>
       <c r="G200" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>8</v>
+        <v>840</v>
       </c>
     </row>
     <row r="201">
@@ -8062,22 +8062,22 @@
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>45607</v>
+        <v>45342</v>
       </c>
       <c r="C201" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D201" t="n">
-        <v>2.405870562118181</v>
+        <v>2.47832820120066</v>
       </c>
       <c r="E201" t="n">
-        <v>3.522627119002715</v>
+        <v>3.450169479920236</v>
       </c>
       <c r="F201" t="n">
-        <v>2.91812056169769</v>
+        <v>4.350487315072731</v>
       </c>
       <c r="G201" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -8095,22 +8095,22 @@
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>45667</v>
+        <v>45355</v>
       </c>
       <c r="C202" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D202" t="n">
-        <v>2.443855155030464</v>
+        <v>2.499070935848451</v>
       </c>
       <c r="E202" t="n">
-        <v>3.484642526090432</v>
+        <v>3.429426745272445</v>
       </c>
       <c r="F202" t="n">
-        <v>2.91812056169769</v>
+        <v>4.350487315072731</v>
       </c>
       <c r="G202" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203">
@@ -8128,22 +8128,22 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>45686</v>
+        <v>45607</v>
       </c>
       <c r="C203" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D203" t="n">
-        <v>2.395352894016685</v>
+        <v>2.405870562118181</v>
       </c>
       <c r="E203" t="n">
-        <v>3.533144787104211</v>
+        <v>3.522627119002715</v>
       </c>
       <c r="F203" t="n">
         <v>2.91812056169769</v>
       </c>
       <c r="G203" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="204">
@@ -8161,22 +8161,22 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>45758</v>
+        <v>45667</v>
       </c>
       <c r="C204" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D204" t="n">
-        <v>2.477713892911565</v>
+        <v>2.443855155030464</v>
       </c>
       <c r="E204" t="n">
-        <v>3.450783788209331</v>
+        <v>3.484642526090432</v>
       </c>
       <c r="F204" t="n">
-        <v>2.52089135996528</v>
+        <v>2.91812056169769</v>
       </c>
       <c r="G204" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="205">
@@ -8194,55 +8194,55 @@
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>45791</v>
+        <v>45686</v>
       </c>
       <c r="C205" t="n">
         <v>5.928497681120896</v>
       </c>
       <c r="D205" t="n">
-        <v>2.410849453867456</v>
+        <v>2.395352894016685</v>
       </c>
       <c r="E205" t="n">
-        <v>3.51764822725344</v>
+        <v>3.533144787104211</v>
       </c>
       <c r="F205" t="n">
-        <v>2.471476860639594</v>
+        <v>2.91812056169769</v>
       </c>
       <c r="G205" t="n">
-        <v>2.298359534275684</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PLTR US Equity</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>45467</v>
+        <v>45758</v>
       </c>
       <c r="C206" t="n">
-        <v>2.661456417025668</v>
+        <v>5.928497681120896</v>
       </c>
       <c r="D206" t="n">
-        <v>2.460299018372195</v>
+        <v>2.477713892911565</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2011573986534732</v>
+        <v>3.450783788209331</v>
       </c>
       <c r="F206" t="n">
-        <v>5.561187113321099</v>
+        <v>2.52089135996528</v>
       </c>
       <c r="G206" t="n">
-        <v>3.990649944335645</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8250,65 +8250,65 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PLTR US Equity</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>45470</v>
+        <v>45791</v>
       </c>
       <c r="C207" t="n">
-        <v>2.661456417025668</v>
+        <v>5.928497681120896</v>
       </c>
       <c r="D207" t="n">
-        <v>2.495014880214741</v>
+        <v>2.410849453867456</v>
       </c>
       <c r="E207" t="n">
-        <v>0.1664415368109271</v>
+        <v>3.51764822725344</v>
       </c>
       <c r="F207" t="n">
-        <v>5.561187113321099</v>
+        <v>2.471476860639594</v>
       </c>
       <c r="G207" t="n">
-        <v>3.990649944335645</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>149</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>43682</v>
+        <v>45467</v>
       </c>
       <c r="C208" t="n">
-        <v>4.339968775751967</v>
+        <v>2.661456417025668</v>
       </c>
       <c r="D208" t="n">
-        <v>2.260269146543943</v>
+        <v>2.460299018372195</v>
       </c>
       <c r="E208" t="n">
-        <v>2.079699629208024</v>
+        <v>0.2011573986534732</v>
       </c>
       <c r="F208" t="n">
-        <v>5.669465567972425</v>
+        <v>5.561187113321099</v>
       </c>
       <c r="G208" t="n">
-        <v>0.8493289320935251</v>
+        <v>4.351995227361876</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8316,32 +8316,32 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>43804</v>
+        <v>45470</v>
       </c>
       <c r="C209" t="n">
-        <v>4.339968775751967</v>
+        <v>2.661456417025668</v>
       </c>
       <c r="D209" t="n">
-        <v>2.499448483176573</v>
+        <v>2.495014880214741</v>
       </c>
       <c r="E209" t="n">
-        <v>1.840520292575394</v>
+        <v>0.1664415368109271</v>
       </c>
       <c r="F209" t="n">
-        <v>5.669465567972425</v>
+        <v>5.561187113321099</v>
       </c>
       <c r="G209" t="n">
-        <v>0.8493289320935251</v>
+        <v>4.351995227361876</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -8359,55 +8359,55 @@
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>44523</v>
+        <v>43682</v>
       </c>
       <c r="C210" t="n">
+        <v>4.339968775751967</v>
+      </c>
+      <c r="D210" t="n">
+        <v>2.260269146543943</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2.079699629208024</v>
+      </c>
+      <c r="F210" t="n">
         <v>5.669465567972425</v>
       </c>
-      <c r="D210" t="n">
-        <v>1.800578755128124</v>
-      </c>
-      <c r="E210" t="n">
-        <v>3.868886812844301</v>
-      </c>
-      <c r="F210" t="n">
-        <v>2.042587311962311</v>
-      </c>
       <c r="G210" t="n">
-        <v>0.8493289320935251</v>
+        <v>0.8537684856989868</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1375</v>
+        <v>119</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RBLX US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>45215</v>
+        <v>43804</v>
       </c>
       <c r="C211" t="n">
-        <v>2.508796338462969</v>
+        <v>4.339968775751967</v>
       </c>
       <c r="D211" t="n">
-        <v>2.484812202783014</v>
+        <v>2.499448483176573</v>
       </c>
       <c r="E211" t="n">
-        <v>0.02398413567995483</v>
+        <v>1.840520292575394</v>
       </c>
       <c r="F211" t="n">
-        <v>5.613864780460612</v>
+        <v>5.669465567972425</v>
       </c>
       <c r="G211" t="n">
-        <v>4.370070549386075</v>
+        <v>0.8537684856989868</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -8415,40 +8415,40 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>RBLX US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>45260</v>
+        <v>44523</v>
       </c>
       <c r="C212" t="n">
-        <v>2.956960427245351</v>
+        <v>5.669465567972425</v>
       </c>
       <c r="D212" t="n">
-        <v>2.483263742202913</v>
+        <v>1.800578755128124</v>
       </c>
       <c r="E212" t="n">
-        <v>0.4736966850424378</v>
+        <v>3.868886812844301</v>
       </c>
       <c r="F212" t="n">
-        <v>5.613864780460612</v>
+        <v>2.042587311962311</v>
       </c>
       <c r="G212" t="n">
-        <v>4.370070549386075</v>
+        <v>0.8537684856989868</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="213">
@@ -8458,22 +8458,22 @@
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>45267</v>
+        <v>45215</v>
       </c>
       <c r="C213" t="n">
-        <v>2.956960427245351</v>
+        <v>2.508796338462969</v>
       </c>
       <c r="D213" t="n">
-        <v>2.486937865677791</v>
+        <v>2.484812202783014</v>
       </c>
       <c r="E213" t="n">
-        <v>0.4700225615675602</v>
+        <v>0.02398413567995483</v>
       </c>
       <c r="F213" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="G213" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -8491,22 +8491,22 @@
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>45280</v>
+        <v>45260</v>
       </c>
       <c r="C214" t="n">
         <v>2.956960427245351</v>
       </c>
       <c r="D214" t="n">
-        <v>2.480229827037564</v>
+        <v>2.483263742202913</v>
       </c>
       <c r="E214" t="n">
-        <v>0.4767306002077873</v>
+        <v>0.4736966850424378</v>
       </c>
       <c r="F214" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="G214" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -8524,22 +8524,22 @@
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>45294</v>
+        <v>45267</v>
       </c>
       <c r="C215" t="n">
         <v>2.956960427245351</v>
       </c>
       <c r="D215" t="n">
-        <v>2.487123308865313</v>
+        <v>2.486937865677791</v>
       </c>
       <c r="E215" t="n">
-        <v>0.4698371183800383</v>
+        <v>0.4700225615675602</v>
       </c>
       <c r="F215" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="G215" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216">
@@ -8557,22 +8557,22 @@
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>45299</v>
+        <v>45280</v>
       </c>
       <c r="C216" t="n">
         <v>2.956960427245351</v>
       </c>
       <c r="D216" t="n">
-        <v>2.482960031547005</v>
+        <v>2.480229827037564</v>
       </c>
       <c r="E216" t="n">
-        <v>0.4740003956983463</v>
+        <v>0.4767306002077873</v>
       </c>
       <c r="F216" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="G216" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
@@ -8590,22 +8590,22 @@
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>45334</v>
+        <v>45294</v>
       </c>
       <c r="C217" t="n">
         <v>2.956960427245351</v>
       </c>
       <c r="D217" t="n">
-        <v>2.436378216247748</v>
+        <v>2.487123308865313</v>
       </c>
       <c r="E217" t="n">
-        <v>0.520582210997603</v>
+        <v>0.4698371183800383</v>
       </c>
       <c r="F217" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="G217" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -8623,22 +8623,22 @@
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>45385</v>
+        <v>45299</v>
       </c>
       <c r="C218" t="n">
         <v>2.956960427245351</v>
       </c>
       <c r="D218" t="n">
-        <v>2.471450474981255</v>
+        <v>2.482960031547005</v>
       </c>
       <c r="E218" t="n">
-        <v>0.485509952264096</v>
+        <v>0.4740003956983463</v>
       </c>
       <c r="F218" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="G218" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -8646,32 +8646,32 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ROKU US Equity</t>
+          <t>RBLX US Equity</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>44939</v>
+        <v>45334</v>
       </c>
       <c r="C219" t="n">
-        <v>2.557799181820416</v>
+        <v>2.956960427245351</v>
       </c>
       <c r="D219" t="n">
-        <v>2.498355085911617</v>
+        <v>2.436378216247748</v>
       </c>
       <c r="E219" t="n">
-        <v>0.05944409590879873</v>
+        <v>0.520582210997603</v>
       </c>
       <c r="F219" t="n">
-        <v>4.155825759621661</v>
+        <v>5.613864780460612</v>
       </c>
       <c r="G219" t="n">
-        <v>3.152581726567422</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -8679,32 +8679,32 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ROKU US Equity</t>
+          <t>RBLX US Equity</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>44944</v>
+        <v>45385</v>
       </c>
       <c r="C220" t="n">
-        <v>2.557799181820416</v>
+        <v>2.956960427245351</v>
       </c>
       <c r="D220" t="n">
-        <v>2.46725106701135</v>
+        <v>2.471450474981255</v>
       </c>
       <c r="E220" t="n">
-        <v>0.09054811480906544</v>
+        <v>0.485509952264096</v>
       </c>
       <c r="F220" t="n">
-        <v>4.155825759621661</v>
+        <v>5.613864780460612</v>
       </c>
       <c r="G220" t="n">
-        <v>3.152581726567422</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -8722,22 +8722,22 @@
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>44951</v>
+        <v>44939</v>
       </c>
       <c r="C221" t="n">
         <v>2.557799181820416</v>
       </c>
       <c r="D221" t="n">
-        <v>2.46510619440055</v>
+        <v>2.498355085911617</v>
       </c>
       <c r="E221" t="n">
-        <v>0.09269298741986587</v>
+        <v>0.05944409590879873</v>
       </c>
       <c r="F221" t="n">
         <v>4.155825759621661</v>
       </c>
       <c r="G221" t="n">
-        <v>3.152581726567422</v>
+        <v>2.804932632280629</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222">
@@ -8755,22 +8755,22 @@
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>45281</v>
+        <v>44944</v>
       </c>
       <c r="C222" t="n">
-        <v>3.768020649354798</v>
+        <v>2.557799181820416</v>
       </c>
       <c r="D222" t="n">
-        <v>2.417125487740297</v>
+        <v>2.46725106701135</v>
       </c>
       <c r="E222" t="n">
-        <v>1.350895161614501</v>
+        <v>0.09054811480906544</v>
       </c>
       <c r="F222" t="n">
         <v>4.155825759621661</v>
       </c>
       <c r="G222" t="n">
-        <v>3.152581726567422</v>
+        <v>2.804932632280629</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -8788,22 +8788,22 @@
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>45288</v>
+        <v>44951</v>
       </c>
       <c r="C223" t="n">
-        <v>3.768020649354798</v>
+        <v>2.557799181820416</v>
       </c>
       <c r="D223" t="n">
-        <v>2.450449174339236</v>
+        <v>2.46510619440055</v>
       </c>
       <c r="E223" t="n">
-        <v>1.317571475015562</v>
+        <v>0.09269298741986587</v>
       </c>
       <c r="F223" t="n">
         <v>4.155825759621661</v>
       </c>
       <c r="G223" t="n">
-        <v>3.152581726567422</v>
+        <v>2.804932632280629</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -8817,26 +8817,26 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>ROKU US Equity</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>44741</v>
+        <v>45281</v>
       </c>
       <c r="C224" t="n">
-        <v>5.620132363709971</v>
+        <v>3.768020649354798</v>
       </c>
       <c r="D224" t="n">
-        <v>1.488441260249933</v>
+        <v>2.417125487740297</v>
       </c>
       <c r="E224" t="n">
-        <v>4.131691103460039</v>
+        <v>1.350895161614501</v>
       </c>
       <c r="F224" t="n">
-        <v>2.91460304516806</v>
+        <v>4.155825759621661</v>
       </c>
       <c r="G224" t="n">
-        <v>2.207612058863048</v>
+        <v>2.804932632280629</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -8844,32 +8844,32 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>ROKU US Equity</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>44782</v>
+        <v>45288</v>
       </c>
       <c r="C225" t="n">
-        <v>5.620132363709971</v>
+        <v>3.768020649354798</v>
       </c>
       <c r="D225" t="n">
-        <v>1.934205141618311</v>
+        <v>2.450449174339236</v>
       </c>
       <c r="E225" t="n">
-        <v>3.68592722209166</v>
+        <v>1.317571475015562</v>
       </c>
       <c r="F225" t="n">
-        <v>2.723243664094936</v>
+        <v>4.155825759621661</v>
       </c>
       <c r="G225" t="n">
-        <v>2.207612058863048</v>
+        <v>2.804932632280629</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>966</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226">
@@ -8887,22 +8887,22 @@
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>45749</v>
+        <v>44741</v>
       </c>
       <c r="C226" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D226" t="n">
-        <v>2.498417588196506</v>
+        <v>1.488441260249933</v>
       </c>
       <c r="E226" t="n">
-        <v>3.121714775513465</v>
+        <v>4.131691103460039</v>
       </c>
       <c r="F226" t="n">
-        <v>2.723243664094936</v>
+        <v>2.91460304516806</v>
       </c>
       <c r="G226" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -8920,22 +8920,22 @@
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>45789</v>
+        <v>44782</v>
       </c>
       <c r="C227" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D227" t="n">
-        <v>2.380006979451712</v>
+        <v>1.934205141618311</v>
       </c>
       <c r="E227" t="n">
-        <v>3.240125384258259</v>
+        <v>3.68592722209166</v>
       </c>
       <c r="F227" t="n">
         <v>2.723243664094936</v>
       </c>
       <c r="G227" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3</v>
+        <v>966</v>
       </c>
     </row>
     <row r="228">
@@ -8953,22 +8953,22 @@
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>45796</v>
+        <v>45749</v>
       </c>
       <c r="C228" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D228" t="n">
-        <v>2.499338796129778</v>
+        <v>2.498417588196506</v>
       </c>
       <c r="E228" t="n">
-        <v>3.120793567580193</v>
+        <v>3.121714775513465</v>
       </c>
       <c r="F228" t="n">
         <v>2.723243664094936</v>
       </c>
       <c r="G228" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="229">
@@ -8986,22 +8986,22 @@
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>45810</v>
+        <v>45789</v>
       </c>
       <c r="C229" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D229" t="n">
-        <v>2.498770488771947</v>
+        <v>2.380006979451712</v>
       </c>
       <c r="E229" t="n">
-        <v>3.121361874938025</v>
+        <v>3.240125384258259</v>
       </c>
       <c r="F229" t="n">
         <v>2.723243664094936</v>
       </c>
       <c r="G229" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
@@ -9019,55 +9019,55 @@
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>45817</v>
+        <v>45796</v>
       </c>
       <c r="C230" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D230" t="n">
-        <v>2.381812167252462</v>
+        <v>2.499338796129778</v>
       </c>
       <c r="E230" t="n">
-        <v>3.238320196457509</v>
+        <v>3.120793567580193</v>
       </c>
       <c r="F230" t="n">
-        <v>2.381812167252462</v>
+        <v>2.723243664094936</v>
       </c>
       <c r="G230" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I230" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SHOP CN Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>43872</v>
+        <v>45810</v>
       </c>
       <c r="C231" t="n">
-        <v>3.192972843460788</v>
+        <v>5.620132363709971</v>
       </c>
       <c r="D231" t="n">
-        <v>2.332751749069724</v>
+        <v>2.498770488771947</v>
       </c>
       <c r="E231" t="n">
-        <v>0.860221094391064</v>
+        <v>3.121361874938025</v>
       </c>
       <c r="F231" t="n">
-        <v>52.2282354545503</v>
+        <v>2.723243664094936</v>
       </c>
       <c r="G231" t="n">
-        <v>9.640717166494472</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9075,65 +9075,65 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>364</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SICPQ US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>44223</v>
+        <v>45817</v>
       </c>
       <c r="C232" t="n">
-        <v>2.610871723727289</v>
+        <v>5.620132363709971</v>
       </c>
       <c r="D232" t="n">
-        <v>2.460555308172743</v>
+        <v>2.381812167252462</v>
       </c>
       <c r="E232" t="n">
-        <v>0.150316415554546</v>
+        <v>3.238320196457509</v>
       </c>
       <c r="F232" t="n">
-        <v>5.12662364125694</v>
+        <v>2.381812167252462</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SICPQ US Equity</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>44326</v>
+        <v>43872</v>
       </c>
       <c r="C233" t="n">
-        <v>5.103562225949012</v>
+        <v>3.192972843460788</v>
       </c>
       <c r="D233" t="n">
-        <v>2.284945336006296</v>
+        <v>2.332751749069724</v>
       </c>
       <c r="E233" t="n">
-        <v>2.818616889942716</v>
+        <v>0.860221094391064</v>
       </c>
       <c r="F233" t="n">
-        <v>5.12662364125694</v>
+        <v>52.2282354545503</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>10.1728501816377</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>147</v>
+        <v>364</v>
       </c>
     </row>
     <row r="234">
@@ -9151,16 +9151,16 @@
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>44475</v>
+        <v>44223</v>
       </c>
       <c r="C234" t="n">
-        <v>5.103562225949012</v>
+        <v>2.610871723727289</v>
       </c>
       <c r="D234" t="n">
-        <v>2.455093706859503</v>
+        <v>2.460555308172743</v>
       </c>
       <c r="E234" t="n">
-        <v>2.648468519089509</v>
+        <v>0.150316415554546</v>
       </c>
       <c r="F234" t="n">
         <v>5.12662364125694</v>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
@@ -9184,20 +9184,20 @@
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>44741</v>
+        <v>44326</v>
       </c>
       <c r="C235" t="n">
+        <v>5.103562225949012</v>
+      </c>
+      <c r="D235" t="n">
+        <v>2.284945336006296</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2.818616889942716</v>
+      </c>
+      <c r="F235" t="n">
         <v>5.12662364125694</v>
       </c>
-      <c r="D235" t="n">
-        <v>1.603607655781641</v>
-      </c>
-      <c r="E235" t="n">
-        <v>3.5230159854753</v>
-      </c>
-      <c r="F235" t="n">
-        <v>4.523329128437432</v>
-      </c>
       <c r="G235" t="n">
         <v>0</v>
       </c>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
     </row>
     <row r="236">
@@ -9217,52 +9217,52 @@
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>44874</v>
+        <v>44475</v>
       </c>
       <c r="C236" t="n">
+        <v>5.103562225949012</v>
+      </c>
+      <c r="D236" t="n">
+        <v>2.455093706859503</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2.648468519089509</v>
+      </c>
+      <c r="F236" t="n">
         <v>5.12662364125694</v>
       </c>
-      <c r="D236" t="n">
-        <v>2.241013464774342</v>
-      </c>
-      <c r="E236" t="n">
-        <v>2.885610176482599</v>
-      </c>
-      <c r="F236" t="n">
-        <v>2.418433759045222</v>
-      </c>
       <c r="G236" t="n">
         <v>0</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SICPQ US Equity</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>44140</v>
+        <v>44741</v>
       </c>
       <c r="C237" t="n">
-        <v>3.026847350995796</v>
+        <v>5.12662364125694</v>
       </c>
       <c r="D237" t="n">
-        <v>2.449333763250188</v>
+        <v>1.603607655781641</v>
       </c>
       <c r="E237" t="n">
-        <v>0.5775135877456079</v>
+        <v>3.5230159854753</v>
       </c>
       <c r="F237" t="n">
-        <v>3.023580224486117</v>
+        <v>4.523329128437432</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -9279,34 +9279,34 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SICPQ US Equity</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>44144</v>
+        <v>44874</v>
       </c>
       <c r="C238" t="n">
-        <v>3.026847350995796</v>
+        <v>5.12662364125694</v>
       </c>
       <c r="D238" t="n">
-        <v>2.482195643686709</v>
+        <v>2.241013464774342</v>
       </c>
       <c r="E238" t="n">
-        <v>0.5446517073090869</v>
+        <v>2.885610176482599</v>
       </c>
       <c r="F238" t="n">
-        <v>3.023580224486117</v>
+        <v>2.418433759045222</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I238" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
     </row>
     <row r="239">
@@ -9316,16 +9316,16 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>44173</v>
+        <v>44140</v>
       </c>
       <c r="C239" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D239" t="n">
-        <v>2.482496124083844</v>
+        <v>2.449333763250188</v>
       </c>
       <c r="E239" t="n">
-        <v>0.5443512269119521</v>
+        <v>0.5775135877456079</v>
       </c>
       <c r="F239" t="n">
         <v>3.023580224486117</v>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -9349,16 +9349,16 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>44181</v>
+        <v>44144</v>
       </c>
       <c r="C240" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D240" t="n">
-        <v>2.499462269039485</v>
+        <v>2.482195643686709</v>
       </c>
       <c r="E240" t="n">
-        <v>0.5273850819563108</v>
+        <v>0.5446517073090869</v>
       </c>
       <c r="F240" t="n">
         <v>3.023580224486117</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241">
@@ -9382,16 +9382,16 @@
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>44186</v>
+        <v>44173</v>
       </c>
       <c r="C241" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D241" t="n">
-        <v>2.4870364768809</v>
+        <v>2.482496124083844</v>
       </c>
       <c r="E241" t="n">
-        <v>0.5398108741148957</v>
+        <v>0.5443512269119521</v>
       </c>
       <c r="F241" t="n">
         <v>3.023580224486117</v>
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -9415,16 +9415,16 @@
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>44209</v>
+        <v>44181</v>
       </c>
       <c r="C242" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D242" t="n">
-        <v>2.447589164732871</v>
+        <v>2.499462269039485</v>
       </c>
       <c r="E242" t="n">
-        <v>0.5792581862629249</v>
+        <v>0.5273850819563108</v>
       </c>
       <c r="F242" t="n">
         <v>3.023580224486117</v>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -9448,16 +9448,16 @@
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>44231</v>
+        <v>44186</v>
       </c>
       <c r="C243" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D243" t="n">
-        <v>2.44834329233853</v>
+        <v>2.4870364768809</v>
       </c>
       <c r="E243" t="n">
-        <v>0.5785040586572658</v>
+        <v>0.5398108741148957</v>
       </c>
       <c r="F243" t="n">
         <v>3.023580224486117</v>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="244">
@@ -9481,16 +9481,16 @@
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>44236</v>
+        <v>44209</v>
       </c>
       <c r="C244" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D244" t="n">
-        <v>2.499265584661426</v>
+        <v>2.447589164732871</v>
       </c>
       <c r="E244" t="n">
-        <v>0.5275817663343698</v>
+        <v>0.5792581862629249</v>
       </c>
       <c r="F244" t="n">
         <v>3.023580224486117</v>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="245">
@@ -9514,16 +9514,16 @@
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>44279</v>
+        <v>44231</v>
       </c>
       <c r="C245" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D245" t="n">
-        <v>2.41401418261613</v>
+        <v>2.44834329233853</v>
       </c>
       <c r="E245" t="n">
-        <v>0.6128331683796659</v>
+        <v>0.5785040586572658</v>
       </c>
       <c r="F245" t="n">
         <v>3.023580224486117</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -9547,55 +9547,55 @@
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>44369</v>
+        <v>44236</v>
       </c>
       <c r="C246" t="n">
         <v>3.026847350995796</v>
       </c>
       <c r="D246" t="n">
-        <v>2.059882616956275</v>
+        <v>2.499265584661426</v>
       </c>
       <c r="E246" t="n">
-        <v>0.9669647340395211</v>
+        <v>0.5275817663343698</v>
       </c>
       <c r="F246" t="n">
-        <v>2.196430239996082</v>
+        <v>3.023580224486117</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I246" t="n">
-        <v>233</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SOFI US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>45351</v>
+        <v>44279</v>
       </c>
       <c r="C247" t="n">
-        <v>2.550706462477966</v>
+        <v>3.026847350995796</v>
       </c>
       <c r="D247" t="n">
-        <v>2.464636007336274</v>
+        <v>2.41401418261613</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0860704551416922</v>
+        <v>0.6128331683796659</v>
       </c>
       <c r="F247" t="n">
-        <v>5.229612458381479</v>
+        <v>3.023580224486117</v>
       </c>
       <c r="G247" t="n">
-        <v>4.218009250574899</v>
+        <v>0</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -9603,40 +9603,40 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SOFI US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>45727</v>
+        <v>44369</v>
       </c>
       <c r="C248" t="n">
-        <v>5.229612458381479</v>
+        <v>3.026847350995796</v>
       </c>
       <c r="D248" t="n">
-        <v>2.472181448703896</v>
+        <v>2.059882616956275</v>
       </c>
       <c r="E248" t="n">
-        <v>2.757431009677583</v>
+        <v>0.9669647340395211</v>
       </c>
       <c r="F248" t="n">
-        <v>4.266684198599797</v>
+        <v>2.196430239996082</v>
       </c>
       <c r="G248" t="n">
-        <v>4.218009250574899</v>
+        <v>0</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2</v>
+        <v>233</v>
       </c>
     </row>
     <row r="249">
@@ -9646,22 +9646,22 @@
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>45751</v>
+        <v>45351</v>
       </c>
       <c r="C249" t="n">
+        <v>2.550706462477966</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2.464636007336274</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0.0860704551416922</v>
+      </c>
+      <c r="F249" t="n">
         <v>5.229612458381479</v>
       </c>
-      <c r="D249" t="n">
-        <v>2.445843300628442</v>
-      </c>
-      <c r="E249" t="n">
-        <v>2.783769157753037</v>
-      </c>
-      <c r="F249" t="n">
-        <v>4.266684198599797</v>
-      </c>
       <c r="G249" t="n">
-        <v>4.218009250574899</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250">
@@ -9679,22 +9679,22 @@
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>45758</v>
+        <v>45727</v>
       </c>
       <c r="C250" t="n">
         <v>5.229612458381479</v>
       </c>
       <c r="D250" t="n">
-        <v>2.418662127939332</v>
+        <v>2.472181448703896</v>
       </c>
       <c r="E250" t="n">
-        <v>2.810950330442147</v>
+        <v>2.757431009677583</v>
       </c>
       <c r="F250" t="n">
-        <v>4.266684198599797</v>
+        <v>4.561807789059414</v>
       </c>
       <c r="G250" t="n">
-        <v>4.218009250574899</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -9712,22 +9712,22 @@
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>45792</v>
+        <v>45751</v>
       </c>
       <c r="C251" t="n">
         <v>5.229612458381479</v>
       </c>
       <c r="D251" t="n">
-        <v>2.481259839201507</v>
+        <v>2.445843300628442</v>
       </c>
       <c r="E251" t="n">
-        <v>2.748352619179972</v>
+        <v>2.783769157753037</v>
       </c>
       <c r="F251" t="n">
-        <v>4.266684198599797</v>
+        <v>4.561807789059414</v>
       </c>
       <c r="G251" t="n">
-        <v>4.218009250574899</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="252">
@@ -9745,22 +9745,22 @@
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>45812</v>
+        <v>45758</v>
       </c>
       <c r="C252" t="n">
         <v>5.229612458381479</v>
       </c>
       <c r="D252" t="n">
-        <v>2.38330156245796</v>
+        <v>2.418662127939332</v>
       </c>
       <c r="E252" t="n">
-        <v>2.846310895923519</v>
+        <v>2.810950330442147</v>
       </c>
       <c r="F252" t="n">
-        <v>4.266684198599797</v>
+        <v>4.561807789059414</v>
       </c>
       <c r="G252" t="n">
-        <v>4.218009250574899</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -9768,32 +9768,32 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SPLK US Equity</t>
+          <t>SOFI US Equity</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>43616</v>
+        <v>45792</v>
       </c>
       <c r="C253" t="n">
-        <v>3.494395670025415</v>
+        <v>5.229612458381479</v>
       </c>
       <c r="D253" t="n">
-        <v>2.485108132712724</v>
+        <v>2.481259839201507</v>
       </c>
       <c r="E253" t="n">
-        <v>1.009287537312691</v>
+        <v>2.748352619179972</v>
       </c>
       <c r="F253" t="n">
-        <v>3.20645869204066</v>
+        <v>4.561807789059414</v>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -9801,32 +9801,32 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SPLK US Equity</t>
+          <t>SOFI US Equity</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>43641</v>
+        <v>45812</v>
       </c>
       <c r="C254" t="n">
-        <v>3.494395670025415</v>
+        <v>5.229612458381479</v>
       </c>
       <c r="D254" t="n">
-        <v>2.452210267079652</v>
+        <v>2.38330156245796</v>
       </c>
       <c r="E254" t="n">
-        <v>1.042185402945763</v>
+        <v>2.846310895923519</v>
       </c>
       <c r="F254" t="n">
-        <v>3.20645869204066</v>
+        <v>4.561807789059414</v>
       </c>
       <c r="G254" t="n">
-        <v>0</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="255">
@@ -9844,16 +9844,16 @@
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>43699</v>
+        <v>43616</v>
       </c>
       <c r="C255" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D255" t="n">
-        <v>2.495398334569602</v>
+        <v>2.485108132712724</v>
       </c>
       <c r="E255" t="n">
-        <v>0.998997335455813</v>
+        <v>1.009287537312691</v>
       </c>
       <c r="F255" t="n">
         <v>3.20645869204066</v>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="256">
@@ -9877,19 +9877,19 @@
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>43888</v>
+        <v>43641</v>
       </c>
       <c r="C256" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D256" t="n">
-        <v>2.450594454730355</v>
+        <v>2.452210267079652</v>
       </c>
       <c r="E256" t="n">
-        <v>1.04380121529506</v>
+        <v>1.042185402945763</v>
       </c>
       <c r="F256" t="n">
-        <v>3.078079371467204</v>
+        <v>3.20645869204066</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -9910,19 +9910,19 @@
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>43902</v>
+        <v>43699</v>
       </c>
       <c r="C257" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D257" t="n">
-        <v>2.441980924906957</v>
+        <v>2.495398334569602</v>
       </c>
       <c r="E257" t="n">
-        <v>1.052414745118458</v>
+        <v>0.998997335455813</v>
       </c>
       <c r="F257" t="n">
-        <v>3.078079371467204</v>
+        <v>3.20645869204066</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -9943,16 +9943,16 @@
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>43906</v>
+        <v>43888</v>
       </c>
       <c r="C258" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D258" t="n">
-        <v>2.373268466536064</v>
+        <v>2.450594454730355</v>
       </c>
       <c r="E258" t="n">
-        <v>1.121127203489351</v>
+        <v>1.04380121529506</v>
       </c>
       <c r="F258" t="n">
         <v>3.078079371467204</v>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="259">
@@ -9976,16 +9976,16 @@
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>43924</v>
+        <v>43902</v>
       </c>
       <c r="C259" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D259" t="n">
-        <v>2.492071191023189</v>
+        <v>2.441980924906957</v>
       </c>
       <c r="E259" t="n">
-        <v>1.002324479002226</v>
+        <v>1.052414745118458</v>
       </c>
       <c r="F259" t="n">
         <v>3.078079371467204</v>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -10009,19 +10009,19 @@
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>44019</v>
+        <v>43906</v>
       </c>
       <c r="C260" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D260" t="n">
-        <v>2.473921695108165</v>
+        <v>2.373268466536064</v>
       </c>
       <c r="E260" t="n">
-        <v>1.02047397491725</v>
+        <v>1.121127203489351</v>
       </c>
       <c r="F260" t="n">
-        <v>2.569739417368445</v>
+        <v>3.078079371467204</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -10042,19 +10042,19 @@
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>44025</v>
+        <v>43924</v>
       </c>
       <c r="C261" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D261" t="n">
-        <v>2.487766524352427</v>
+        <v>2.492071191023189</v>
       </c>
       <c r="E261" t="n">
-        <v>1.006629145672988</v>
+        <v>1.002324479002226</v>
       </c>
       <c r="F261" t="n">
-        <v>2.531370347864764</v>
+        <v>3.078079371467204</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
@@ -10075,19 +10075,19 @@
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>44033</v>
+        <v>44019</v>
       </c>
       <c r="C262" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D262" t="n">
-        <v>2.463201910345469</v>
+        <v>2.473921695108165</v>
       </c>
       <c r="E262" t="n">
-        <v>1.031193759679946</v>
+        <v>1.02047397491725</v>
       </c>
       <c r="F262" t="n">
-        <v>2.531370347864764</v>
+        <v>2.569739417368445</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -10108,16 +10108,16 @@
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>44039</v>
+        <v>44025</v>
       </c>
       <c r="C263" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D263" t="n">
-        <v>2.492462163706895</v>
+        <v>2.487766524352427</v>
       </c>
       <c r="E263" t="n">
-        <v>1.00193350631852</v>
+        <v>1.006629145672988</v>
       </c>
       <c r="F263" t="n">
         <v>2.531370347864764</v>
@@ -10141,52 +10141,52 @@
         </is>
       </c>
       <c r="B264" s="2" t="n">
-        <v>44043</v>
+        <v>44033</v>
       </c>
       <c r="C264" t="n">
         <v>3.494395670025415</v>
       </c>
       <c r="D264" t="n">
-        <v>2.464795473160224</v>
+        <v>2.463201910345469</v>
       </c>
       <c r="E264" t="n">
-        <v>1.029600196865191</v>
+        <v>1.031193759679946</v>
       </c>
       <c r="F264" t="n">
-        <v>2.464795473160224</v>
+        <v>2.531370347864764</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I264" t="n">
-        <v>256</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>STNE US Equity</t>
+          <t>SPLK US Equity</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>44741</v>
+        <v>44039</v>
       </c>
       <c r="C265" t="n">
-        <v>3.297182403513364</v>
+        <v>3.494395670025415</v>
       </c>
       <c r="D265" t="n">
-        <v>1.391236366867092</v>
+        <v>2.492462163706895</v>
       </c>
       <c r="E265" t="n">
-        <v>1.905946036646272</v>
+        <v>1.00193350631852</v>
       </c>
       <c r="F265" t="n">
-        <v>4.037256922425841</v>
+        <v>2.531370347864764</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -10203,34 +10203,34 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>STNE US Equity</t>
+          <t>SPLK US Equity</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>44986</v>
+        <v>44043</v>
       </c>
       <c r="C266" t="n">
-        <v>4.037256922425841</v>
+        <v>3.494395670025415</v>
       </c>
       <c r="D266" t="n">
-        <v>2.498411230975241</v>
+        <v>2.464795473160224</v>
       </c>
       <c r="E266" t="n">
-        <v>1.5388456914506</v>
+        <v>1.029600196865191</v>
       </c>
       <c r="F266" t="n">
-        <v>4.000497590018662</v>
+        <v>2.464795473160224</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I266" t="n">
-        <v>6</v>
+        <v>256</v>
       </c>
     </row>
     <row r="267">
@@ -10240,20 +10240,20 @@
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>45338</v>
+        <v>44741</v>
       </c>
       <c r="C267" t="n">
+        <v>3.297182403513364</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1.391236366867092</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.905946036646272</v>
+      </c>
+      <c r="F267" t="n">
         <v>4.037256922425841</v>
       </c>
-      <c r="D267" t="n">
-        <v>2.492975151806824</v>
-      </c>
-      <c r="E267" t="n">
-        <v>1.544281770619017</v>
-      </c>
-      <c r="F267" t="n">
-        <v>2.520105853013299</v>
-      </c>
       <c r="G267" t="n">
         <v>0</v>
       </c>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -10273,151 +10273,151 @@
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>45348</v>
+        <v>44986</v>
       </c>
       <c r="C268" t="n">
         <v>4.037256922425841</v>
       </c>
       <c r="D268" t="n">
-        <v>2.332859152157751</v>
+        <v>2.498411230975241</v>
       </c>
       <c r="E268" t="n">
-        <v>1.70439777026809</v>
+        <v>1.5388456914506</v>
       </c>
       <c r="F268" t="n">
-        <v>2.332859152157751</v>
+        <v>4.000497590018662</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I268" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TCEHY US Equity</t>
+          <t>STNE US Equity</t>
         </is>
       </c>
       <c r="B269" s="2" t="n">
-        <v>44403</v>
+        <v>45338</v>
       </c>
       <c r="C269" t="n">
-        <v>6.721443075616359</v>
+        <v>4.037256922425841</v>
       </c>
       <c r="D269" t="n">
-        <v>2.367571064636416</v>
+        <v>2.492975151806824</v>
       </c>
       <c r="E269" t="n">
-        <v>4.353872010979943</v>
+        <v>1.544281770619017</v>
       </c>
       <c r="F269" t="n">
-        <v>2.367571064636416</v>
+        <v>2.520105853013299</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I269" t="n">
-        <v>189</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>STNE US Equity</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>44349</v>
+        <v>45348</v>
       </c>
       <c r="C270" t="n">
-        <v>2.563272670685783</v>
+        <v>4.037256922425841</v>
       </c>
       <c r="D270" t="n">
-        <v>2.443550473676679</v>
+        <v>2.332859152157751</v>
       </c>
       <c r="E270" t="n">
-        <v>0.119722197009104</v>
+        <v>1.70439777026809</v>
       </c>
       <c r="F270" t="n">
-        <v>3.044362741630565</v>
+        <v>2.332859152157751</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I270" t="n">
-        <v>183</v>
+        <v>72</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TCEHY US Equity</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>44533</v>
+        <v>44403</v>
       </c>
       <c r="C271" t="n">
-        <v>2.573179161192897</v>
+        <v>6.721443075616359</v>
       </c>
       <c r="D271" t="n">
-        <v>2.49772798726607</v>
+        <v>2.367571064636416</v>
       </c>
       <c r="E271" t="n">
-        <v>0.07545117392682688</v>
+        <v>4.353872010979943</v>
       </c>
       <c r="F271" t="n">
-        <v>3.044362741630565</v>
+        <v>2.367571064636416</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I271" t="n">
-        <v>3</v>
+        <v>189</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>44537</v>
+        <v>44435</v>
       </c>
       <c r="C272" t="n">
-        <v>2.673401269490484</v>
+        <v>2.510641850648766</v>
       </c>
       <c r="D272" t="n">
-        <v>2.403895292053794</v>
+        <v>2.480961670814475</v>
       </c>
       <c r="E272" t="n">
-        <v>0.2695059774366899</v>
+        <v>0.0296801798342905</v>
       </c>
       <c r="F272" t="n">
-        <v>3.044362741630565</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -10428,29 +10428,29 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>44553</v>
+        <v>44741</v>
       </c>
       <c r="C273" t="n">
-        <v>2.673401269490484</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D273" t="n">
-        <v>2.499266643036517</v>
+        <v>1.858104784625591</v>
       </c>
       <c r="E273" t="n">
-        <v>0.1741346264539669</v>
+        <v>2.573233917556688</v>
       </c>
       <c r="F273" t="n">
-        <v>3.044362741630565</v>
+        <v>4.129838151132731</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -10461,29 +10461,29 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>44560</v>
+        <v>45077</v>
       </c>
       <c r="C274" t="n">
-        <v>2.673401269490484</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D274" t="n">
-        <v>2.494657656142778</v>
+        <v>2.447227434003666</v>
       </c>
       <c r="E274" t="n">
-        <v>0.1787436133477058</v>
+        <v>1.984111268178613</v>
       </c>
       <c r="F274" t="n">
-        <v>3.044362741630565</v>
+        <v>2.661604462242534</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -10494,29 +10494,29 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>44580</v>
+        <v>45089</v>
       </c>
       <c r="C275" t="n">
-        <v>2.75099439573009</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D275" t="n">
-        <v>2.311629799311019</v>
+        <v>2.495201950495979</v>
       </c>
       <c r="E275" t="n">
-        <v>0.4393645964190709</v>
+        <v>1.9361367516863</v>
       </c>
       <c r="F275" t="n">
-        <v>3.044362741630565</v>
+        <v>2.661604462242534</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -10527,29 +10527,29 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>44586</v>
+        <v>45113</v>
       </c>
       <c r="C276" t="n">
-        <v>2.75099439573009</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D276" t="n">
-        <v>2.306701023343306</v>
+        <v>2.456182008917936</v>
       </c>
       <c r="E276" t="n">
-        <v>0.4442933723867841</v>
+        <v>1.975156693264343</v>
       </c>
       <c r="F276" t="n">
-        <v>3.044362741630565</v>
+        <v>2.661604462242534</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -10560,29 +10560,29 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>44601</v>
+        <v>45140</v>
       </c>
       <c r="C277" t="n">
-        <v>3.044362741630565</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D277" t="n">
-        <v>2.440740616756236</v>
+        <v>2.47090633610732</v>
       </c>
       <c r="E277" t="n">
-        <v>0.6036221248743292</v>
+        <v>1.960432366074959</v>
       </c>
       <c r="F277" t="n">
-        <v>2.821970417975426</v>
+        <v>2.542696852810457</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -10593,29 +10593,29 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>44607</v>
+        <v>45146</v>
       </c>
       <c r="C278" t="n">
-        <v>3.044362741630565</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D278" t="n">
-        <v>2.475131910890901</v>
+        <v>2.47233547965084</v>
       </c>
       <c r="E278" t="n">
-        <v>0.5692308307396639</v>
+        <v>1.959003222531439</v>
       </c>
       <c r="F278" t="n">
-        <v>2.60932238693886</v>
+        <v>2.542696852810457</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -10626,40 +10626,40 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TCS LI Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>44614</v>
+        <v>45149</v>
       </c>
       <c r="C279" t="n">
-        <v>3.044362741630565</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D279" t="n">
-        <v>2.476211833929994</v>
+        <v>2.443826473697707</v>
       </c>
       <c r="E279" t="n">
-        <v>0.5681509077005713</v>
+        <v>1.987512228484572</v>
       </c>
       <c r="F279" t="n">
-        <v>2.476211833929994</v>
+        <v>2.516654055119506</v>
       </c>
       <c r="G279" t="n">
         <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I279" t="n">
-        <v>660</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -10669,55 +10669,55 @@
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>44435</v>
+        <v>45160</v>
       </c>
       <c r="C280" t="n">
-        <v>2.510641850648766</v>
+        <v>4.431338702182279</v>
       </c>
       <c r="D280" t="n">
-        <v>2.480961670814475</v>
+        <v>2.49196636847213</v>
       </c>
       <c r="E280" t="n">
-        <v>0.0296801798342905</v>
+        <v>1.939372333710149</v>
       </c>
       <c r="F280" t="n">
-        <v>4.431338702182279</v>
+        <v>2.49196636847213</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>3</v>
+        <v>316</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>44741</v>
+        <v>44683</v>
       </c>
       <c r="C281" t="n">
-        <v>4.431338702182279</v>
+        <v>2.59792195981262</v>
       </c>
       <c r="D281" t="n">
-        <v>1.858104784625591</v>
+        <v>2.467983523605949</v>
       </c>
       <c r="E281" t="n">
-        <v>2.573233917556688</v>
+        <v>0.1299384362066709</v>
       </c>
       <c r="F281" t="n">
-        <v>4.129838151132731</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -10725,32 +10725,32 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>45077</v>
+        <v>44719</v>
       </c>
       <c r="C282" t="n">
-        <v>4.431338702182279</v>
+        <v>2.59792195981262</v>
       </c>
       <c r="D282" t="n">
-        <v>2.447227434003666</v>
+        <v>2.419180978731964</v>
       </c>
       <c r="E282" t="n">
-        <v>1.984111268178613</v>
+        <v>0.1787409810806557</v>
       </c>
       <c r="F282" t="n">
-        <v>2.661604462242534</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -10758,32 +10758,32 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>45089</v>
+        <v>44728</v>
       </c>
       <c r="C283" t="n">
-        <v>4.431338702182279</v>
+        <v>2.59792195981262</v>
       </c>
       <c r="D283" t="n">
-        <v>2.495201950495979</v>
+        <v>2.404672883499312</v>
       </c>
       <c r="E283" t="n">
-        <v>1.9361367516863</v>
+        <v>0.1932490763133079</v>
       </c>
       <c r="F283" t="n">
-        <v>2.661604462242534</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -10791,32 +10791,32 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>45113</v>
+        <v>44757</v>
       </c>
       <c r="C284" t="n">
-        <v>4.431338702182279</v>
+        <v>2.59792195981262</v>
       </c>
       <c r="D284" t="n">
-        <v>2.456182008917936</v>
+        <v>2.438659762054466</v>
       </c>
       <c r="E284" t="n">
-        <v>1.975156693264343</v>
+        <v>0.1592621977581539</v>
       </c>
       <c r="F284" t="n">
-        <v>2.661604462242534</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -10824,32 +10824,32 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>45140</v>
+        <v>44999</v>
       </c>
       <c r="C285" t="n">
-        <v>4.431338702182279</v>
+        <v>4.322663876455713</v>
       </c>
       <c r="D285" t="n">
-        <v>2.47090633610732</v>
+        <v>2.316948933539472</v>
       </c>
       <c r="E285" t="n">
-        <v>1.960432366074959</v>
+        <v>2.005714942916241</v>
       </c>
       <c r="F285" t="n">
-        <v>2.542696852810457</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -10857,32 +10857,32 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>45146</v>
+        <v>45061</v>
       </c>
       <c r="C286" t="n">
-        <v>4.431338702182279</v>
+        <v>4.322663876455713</v>
       </c>
       <c r="D286" t="n">
-        <v>2.47233547965084</v>
+        <v>2.424121864469815</v>
       </c>
       <c r="E286" t="n">
-        <v>1.959003222531439</v>
+        <v>1.898542011985898</v>
       </c>
       <c r="F286" t="n">
-        <v>2.542696852810457</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -10896,26 +10896,26 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>45149</v>
+        <v>45127</v>
       </c>
       <c r="C287" t="n">
-        <v>4.431338702182279</v>
+        <v>4.322663876455713</v>
       </c>
       <c r="D287" t="n">
-        <v>2.443826473697707</v>
+        <v>2.356034415689819</v>
       </c>
       <c r="E287" t="n">
-        <v>1.987512228484572</v>
+        <v>1.966629460765894</v>
       </c>
       <c r="F287" t="n">
-        <v>2.516654055119506</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -10923,40 +10923,40 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>45160</v>
+        <v>45180</v>
       </c>
       <c r="C288" t="n">
-        <v>4.431338702182279</v>
+        <v>4.322663876455713</v>
       </c>
       <c r="D288" t="n">
-        <v>2.49196636847213</v>
+        <v>2.465314204966026</v>
       </c>
       <c r="E288" t="n">
-        <v>1.939372333710149</v>
+        <v>1.857349671489687</v>
       </c>
       <c r="F288" t="n">
-        <v>2.49196636847213</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I288" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -10966,22 +10966,22 @@
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>44683</v>
+        <v>45204</v>
       </c>
       <c r="C289" t="n">
-        <v>2.59792195981262</v>
+        <v>4.322663876455713</v>
       </c>
       <c r="D289" t="n">
-        <v>2.467983523605949</v>
+        <v>2.491168363395623</v>
       </c>
       <c r="E289" t="n">
-        <v>0.1299384362066709</v>
+        <v>1.83149551306009</v>
       </c>
       <c r="F289" t="n">
         <v>5.581807858149219</v>
       </c>
       <c r="G289" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -10999,22 +10999,22 @@
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>44719</v>
+        <v>45240</v>
       </c>
       <c r="C290" t="n">
-        <v>2.59792195981262</v>
+        <v>4.322663876455713</v>
       </c>
       <c r="D290" t="n">
-        <v>2.419180978731964</v>
+        <v>2.354380326808429</v>
       </c>
       <c r="E290" t="n">
-        <v>0.1787409810806557</v>
+        <v>1.968283549647284</v>
       </c>
       <c r="F290" t="n">
         <v>5.581807858149219</v>
       </c>
       <c r="G290" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -11022,32 +11022,32 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>44728</v>
+        <v>43671</v>
       </c>
       <c r="C291" t="n">
-        <v>2.59792195981262</v>
+        <v>6.743392425454591</v>
       </c>
       <c r="D291" t="n">
-        <v>2.404672883499312</v>
+        <v>2.442817348433947</v>
       </c>
       <c r="E291" t="n">
-        <v>0.1932490763133079</v>
+        <v>4.300575077020644</v>
       </c>
       <c r="F291" t="n">
-        <v>5.581807858149219</v>
+        <v>5.503534374600851</v>
       </c>
       <c r="G291" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -11055,32 +11055,32 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>44757</v>
+        <v>43696</v>
       </c>
       <c r="C292" t="n">
-        <v>2.59792195981262</v>
+        <v>6.743392425454591</v>
       </c>
       <c r="D292" t="n">
-        <v>2.438659762054466</v>
+        <v>2.491729383498323</v>
       </c>
       <c r="E292" t="n">
-        <v>0.1592621977581539</v>
+        <v>4.251663041956268</v>
       </c>
       <c r="F292" t="n">
-        <v>5.581807858149219</v>
+        <v>5.503534374600851</v>
       </c>
       <c r="G292" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -11088,65 +11088,65 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>44999</v>
+        <v>44193</v>
       </c>
       <c r="C293" t="n">
-        <v>4.322663876455713</v>
+        <v>6.743392425454591</v>
       </c>
       <c r="D293" t="n">
-        <v>2.316948933539472</v>
+        <v>2.466786840134851</v>
       </c>
       <c r="E293" t="n">
-        <v>2.005714942916241</v>
+        <v>4.276605585319739</v>
       </c>
       <c r="F293" t="n">
-        <v>5.581807858149219</v>
+        <v>2.466786840134851</v>
       </c>
       <c r="G293" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I293" t="n">
-        <v>58</v>
+        <v>143</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>45061</v>
+        <v>43972</v>
       </c>
       <c r="C294" t="n">
-        <v>4.322663876455713</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D294" t="n">
-        <v>2.424121864469815</v>
+        <v>2.029334861017921</v>
       </c>
       <c r="E294" t="n">
-        <v>1.898542011985898</v>
+        <v>1.21864102061572</v>
       </c>
       <c r="F294" t="n">
-        <v>5.581807858149219</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G294" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -11154,32 +11154,32 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>45127</v>
+        <v>44137</v>
       </c>
       <c r="C295" t="n">
-        <v>4.322663876455713</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D295" t="n">
-        <v>2.356034415689819</v>
+        <v>2.490690629904753</v>
       </c>
       <c r="E295" t="n">
-        <v>1.966629460765894</v>
+        <v>0.7572852517288879</v>
       </c>
       <c r="F295" t="n">
-        <v>5.581807858149219</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G295" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -11187,32 +11187,32 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>45180</v>
+        <v>44141</v>
       </c>
       <c r="C296" t="n">
-        <v>4.322663876455713</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D296" t="n">
-        <v>2.465314204966026</v>
+        <v>2.38687539377013</v>
       </c>
       <c r="E296" t="n">
-        <v>1.857349671489687</v>
+        <v>0.8611004878635109</v>
       </c>
       <c r="F296" t="n">
-        <v>5.581807858149219</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G296" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -11220,32 +11220,32 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>45204</v>
+        <v>44172</v>
       </c>
       <c r="C297" t="n">
-        <v>4.322663876455713</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D297" t="n">
-        <v>2.491168363395623</v>
+        <v>2.448307046106218</v>
       </c>
       <c r="E297" t="n">
-        <v>1.83149551306009</v>
+        <v>0.7996688355274228</v>
       </c>
       <c r="F297" t="n">
-        <v>5.581807858149219</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G297" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -11253,32 +11253,32 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
-        <v>45240</v>
+        <v>44202</v>
       </c>
       <c r="C298" t="n">
-        <v>4.322663876455713</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D298" t="n">
-        <v>2.354380326808429</v>
+        <v>2.486370047835816</v>
       </c>
       <c r="E298" t="n">
-        <v>1.968283549647284</v>
+        <v>0.7616058337978249</v>
       </c>
       <c r="F298" t="n">
-        <v>5.581807858149219</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G298" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -11286,29 +11286,29 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B299" s="2" t="n">
-        <v>43671</v>
+        <v>44222</v>
       </c>
       <c r="C299" t="n">
-        <v>6.743392425454591</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D299" t="n">
-        <v>2.442817348433947</v>
+        <v>2.477842628517131</v>
       </c>
       <c r="E299" t="n">
-        <v>4.300575077020644</v>
+        <v>0.7701332531165099</v>
       </c>
       <c r="F299" t="n">
-        <v>5.503534374600851</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -11319,29 +11319,29 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B300" s="2" t="n">
-        <v>43696</v>
+        <v>44243</v>
       </c>
       <c r="C300" t="n">
-        <v>6.743392425454591</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D300" t="n">
-        <v>2.491729383498323</v>
+        <v>2.44866703314993</v>
       </c>
       <c r="E300" t="n">
-        <v>4.251663041956268</v>
+        <v>0.7993088484837112</v>
       </c>
       <c r="F300" t="n">
-        <v>5.503534374600851</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G300" t="n">
         <v>0</v>
@@ -11352,40 +11352,40 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B301" s="2" t="n">
-        <v>44193</v>
+        <v>44258</v>
       </c>
       <c r="C301" t="n">
-        <v>6.743392425454591</v>
+        <v>3.247975881633641</v>
       </c>
       <c r="D301" t="n">
-        <v>2.466786840134851</v>
+        <v>2.474808192272912</v>
       </c>
       <c r="E301" t="n">
-        <v>4.276605585319739</v>
+        <v>0.7731676893607289</v>
       </c>
       <c r="F301" t="n">
-        <v>2.466786840134851</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="G301" t="n">
         <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I301" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
     </row>
     <row r="302">
@@ -11395,16 +11395,16 @@
         </is>
       </c>
       <c r="B302" s="2" t="n">
-        <v>43972</v>
+        <v>44273</v>
       </c>
       <c r="C302" t="n">
         <v>3.247975881633641</v>
       </c>
       <c r="D302" t="n">
-        <v>2.029334861017921</v>
+        <v>2.494291646161456</v>
       </c>
       <c r="E302" t="n">
-        <v>1.21864102061572</v>
+        <v>0.7536842354721847</v>
       </c>
       <c r="F302" t="n">
         <v>8.598499657580531</v>
@@ -11418,7 +11418,7 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>134</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303">
@@ -11428,16 +11428,16 @@
         </is>
       </c>
       <c r="B303" s="2" t="n">
-        <v>44137</v>
+        <v>44279</v>
       </c>
       <c r="C303" t="n">
         <v>3.247975881633641</v>
       </c>
       <c r="D303" t="n">
-        <v>2.490690629904753</v>
+        <v>2.443091497070741</v>
       </c>
       <c r="E303" t="n">
-        <v>0.7572852517288879</v>
+        <v>0.8048843845629001</v>
       </c>
       <c r="F303" t="n">
         <v>8.598499657580531</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="304">
@@ -11461,16 +11461,16 @@
         </is>
       </c>
       <c r="B304" s="2" t="n">
-        <v>44141</v>
+        <v>44292</v>
       </c>
       <c r="C304" t="n">
         <v>3.247975881633641</v>
       </c>
       <c r="D304" t="n">
-        <v>2.38687539377013</v>
+        <v>2.485240331323569</v>
       </c>
       <c r="E304" t="n">
-        <v>0.8611004878635109</v>
+        <v>0.7627355503100719</v>
       </c>
       <c r="F304" t="n">
         <v>8.598499657580531</v>
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -11494,16 +11494,16 @@
         </is>
       </c>
       <c r="B305" s="2" t="n">
-        <v>44172</v>
+        <v>44322</v>
       </c>
       <c r="C305" t="n">
         <v>3.247975881633641</v>
       </c>
       <c r="D305" t="n">
-        <v>2.448307046106218</v>
+        <v>2.317637879428046</v>
       </c>
       <c r="E305" t="n">
-        <v>0.7996688355274228</v>
+        <v>0.9303380022055951</v>
       </c>
       <c r="F305" t="n">
         <v>8.598499657580531</v>
@@ -11517,7 +11517,7 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
@@ -11527,52 +11527,52 @@
         </is>
       </c>
       <c r="B306" s="2" t="n">
-        <v>44202</v>
+        <v>45376</v>
       </c>
       <c r="C306" t="n">
-        <v>3.247975881633641</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="D306" t="n">
-        <v>2.486370047835816</v>
+        <v>2.392052819615359</v>
       </c>
       <c r="E306" t="n">
-        <v>0.7616058337978249</v>
+        <v>6.206446837965172</v>
       </c>
       <c r="F306" t="n">
-        <v>8.598499657580531</v>
+        <v>2.392052819615359</v>
       </c>
       <c r="G306" t="n">
         <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I306" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>WDAY US Equity</t>
         </is>
       </c>
       <c r="B307" s="2" t="n">
-        <v>44222</v>
+        <v>44557</v>
       </c>
       <c r="C307" t="n">
-        <v>3.247975881633641</v>
+        <v>2.565004471821445</v>
       </c>
       <c r="D307" t="n">
-        <v>2.477842628517131</v>
+        <v>2.477322412588824</v>
       </c>
       <c r="E307" t="n">
-        <v>0.7701332531165099</v>
+        <v>0.08768205923262107</v>
       </c>
       <c r="F307" t="n">
-        <v>8.598499657580531</v>
+        <v>2.558564914762852</v>
       </c>
       <c r="G307" t="n">
         <v>0</v>
@@ -11589,23 +11589,23 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>WDAY US Equity</t>
         </is>
       </c>
       <c r="B308" s="2" t="n">
-        <v>44243</v>
+        <v>44561</v>
       </c>
       <c r="C308" t="n">
-        <v>3.247975881633641</v>
+        <v>2.565004471821445</v>
       </c>
       <c r="D308" t="n">
-        <v>2.44866703314993</v>
+        <v>2.48807326196905</v>
       </c>
       <c r="E308" t="n">
-        <v>0.7993088484837112</v>
+        <v>0.0769312098523951</v>
       </c>
       <c r="F308" t="n">
-        <v>8.598499657580531</v>
+        <v>2.558564914762852</v>
       </c>
       <c r="G308" t="n">
         <v>0</v>
@@ -11616,65 +11616,65 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>WDAY US Equity</t>
         </is>
       </c>
       <c r="B309" s="2" t="n">
-        <v>44258</v>
+        <v>44572</v>
       </c>
       <c r="C309" t="n">
-        <v>3.247975881633641</v>
+        <v>2.565004471821445</v>
       </c>
       <c r="D309" t="n">
-        <v>2.474808192272912</v>
+        <v>1.597830481148872</v>
       </c>
       <c r="E309" t="n">
-        <v>0.7731676893607289</v>
+        <v>0.9671739906725731</v>
       </c>
       <c r="F309" t="n">
-        <v>8.598499657580531</v>
+        <v>1.808907065913188</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I309" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>Z US Equity</t>
         </is>
       </c>
       <c r="B310" s="2" t="n">
-        <v>44273</v>
+        <v>44518</v>
       </c>
       <c r="C310" t="n">
-        <v>3.247975881633641</v>
+        <v>6.609626940393729</v>
       </c>
       <c r="D310" t="n">
-        <v>2.494291646161456</v>
+        <v>2.495336429109796</v>
       </c>
       <c r="E310" t="n">
-        <v>0.7536842354721847</v>
+        <v>4.114290511283933</v>
       </c>
       <c r="F310" t="n">
-        <v>8.598499657580531</v>
+        <v>4.02375816608119</v>
       </c>
       <c r="G310" t="n">
-        <v>0</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -11682,32 +11682,32 @@
         </is>
       </c>
       <c r="I310" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>Z US Equity</t>
         </is>
       </c>
       <c r="B311" s="2" t="n">
-        <v>44279</v>
+        <v>44530</v>
       </c>
       <c r="C311" t="n">
-        <v>3.247975881633641</v>
+        <v>6.609626940393729</v>
       </c>
       <c r="D311" t="n">
-        <v>2.443091497070741</v>
+        <v>2.439183824286375</v>
       </c>
       <c r="E311" t="n">
-        <v>0.8048843845629001</v>
+        <v>4.170443116107354</v>
       </c>
       <c r="F311" t="n">
-        <v>8.598499657580531</v>
+        <v>4.02375816608119</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -11715,32 +11715,32 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>Z US Equity</t>
         </is>
       </c>
       <c r="B312" s="2" t="n">
-        <v>44322</v>
+        <v>44741</v>
       </c>
       <c r="C312" t="n">
-        <v>3.247975881633641</v>
+        <v>6.609626940393729</v>
       </c>
       <c r="D312" t="n">
-        <v>2.317637879428046</v>
+        <v>1.703703887332512</v>
       </c>
       <c r="E312" t="n">
-        <v>0.9303380022055951</v>
+        <v>4.905923053061216</v>
       </c>
       <c r="F312" t="n">
-        <v>8.598499657580531</v>
+        <v>3.978237253304214</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -11748,271 +11748,40 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>Z US Equity</t>
         </is>
       </c>
       <c r="B313" s="2" t="n">
-        <v>45376</v>
+        <v>44918</v>
       </c>
       <c r="C313" t="n">
-        <v>8.598499657580531</v>
+        <v>6.609626940393729</v>
       </c>
       <c r="D313" t="n">
-        <v>2.392052819615359</v>
+        <v>2.237766790295359</v>
       </c>
       <c r="E313" t="n">
-        <v>6.206446837965172</v>
+        <v>4.371860150098369</v>
       </c>
       <c r="F313" t="n">
-        <v>2.392052819615359</v>
+        <v>2.237766790295359</v>
       </c>
       <c r="G313" t="n">
-        <v>0</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I313" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>WDAY US Equity</t>
-        </is>
-      </c>
-      <c r="B314" s="2" t="n">
-        <v>44557</v>
-      </c>
-      <c r="C314" t="n">
-        <v>2.565004471821445</v>
-      </c>
-      <c r="D314" t="n">
-        <v>2.477322412588824</v>
-      </c>
-      <c r="E314" t="n">
-        <v>0.08768205923262107</v>
-      </c>
-      <c r="F314" t="n">
-        <v>2.558564914762852</v>
-      </c>
-      <c r="G314" t="n">
-        <v>0</v>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>Recovered to Large</t>
-        </is>
-      </c>
-      <c r="I314" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>WDAY US Equity</t>
-        </is>
-      </c>
-      <c r="B315" s="2" t="n">
-        <v>44561</v>
-      </c>
-      <c r="C315" t="n">
-        <v>2.565004471821445</v>
-      </c>
-      <c r="D315" t="n">
-        <v>2.48807326196905</v>
-      </c>
-      <c r="E315" t="n">
-        <v>0.0769312098523951</v>
-      </c>
-      <c r="F315" t="n">
-        <v>2.558564914762852</v>
-      </c>
-      <c r="G315" t="n">
-        <v>0</v>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>Recovered to Large</t>
-        </is>
-      </c>
-      <c r="I315" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>WDAY US Equity</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="n">
-        <v>44572</v>
-      </c>
-      <c r="C316" t="n">
-        <v>2.565004471821445</v>
-      </c>
-      <c r="D316" t="n">
-        <v>1.597830481148872</v>
-      </c>
-      <c r="E316" t="n">
-        <v>0.9671739906725731</v>
-      </c>
-      <c r="F316" t="n">
-        <v>1.808907065913188</v>
-      </c>
-      <c r="G316" t="n">
-        <v>0</v>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>Dropped</t>
-        </is>
-      </c>
-      <c r="I316" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Z US Equity</t>
-        </is>
-      </c>
-      <c r="B317" s="2" t="n">
-        <v>44518</v>
-      </c>
-      <c r="C317" t="n">
-        <v>6.609626940393729</v>
-      </c>
-      <c r="D317" t="n">
-        <v>2.495336429109796</v>
-      </c>
-      <c r="E317" t="n">
-        <v>4.114290511283933</v>
-      </c>
-      <c r="F317" t="n">
-        <v>4.02375816608119</v>
-      </c>
-      <c r="G317" t="n">
-        <v>1.681352326847488</v>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>Recovered to Large</t>
-        </is>
-      </c>
-      <c r="I317" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Z US Equity</t>
-        </is>
-      </c>
-      <c r="B318" s="2" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C318" t="n">
-        <v>6.609626940393729</v>
-      </c>
-      <c r="D318" t="n">
-        <v>2.439183824286375</v>
-      </c>
-      <c r="E318" t="n">
-        <v>4.170443116107354</v>
-      </c>
-      <c r="F318" t="n">
-        <v>4.02375816608119</v>
-      </c>
-      <c r="G318" t="n">
-        <v>1.681352326847488</v>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>Recovered to Large</t>
-        </is>
-      </c>
-      <c r="I318" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Z US Equity</t>
-        </is>
-      </c>
-      <c r="B319" s="2" t="n">
-        <v>44741</v>
-      </c>
-      <c r="C319" t="n">
-        <v>6.609626940393729</v>
-      </c>
-      <c r="D319" t="n">
-        <v>1.703703887332512</v>
-      </c>
-      <c r="E319" t="n">
-        <v>4.905923053061216</v>
-      </c>
-      <c r="F319" t="n">
-        <v>3.978237253304214</v>
-      </c>
-      <c r="G319" t="n">
-        <v>1.681352326847488</v>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>Recovered to Large</t>
-        </is>
-      </c>
-      <c r="I319" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Z US Equity</t>
-        </is>
-      </c>
-      <c r="B320" s="2" t="n">
-        <v>44918</v>
-      </c>
-      <c r="C320" t="n">
-        <v>6.609626940393729</v>
-      </c>
-      <c r="D320" t="n">
-        <v>2.237766790295359</v>
-      </c>
-      <c r="E320" t="n">
-        <v>4.371860150098369</v>
-      </c>
-      <c r="F320" t="n">
-        <v>2.237766790295359</v>
-      </c>
-      <c r="G320" t="n">
-        <v>1.681352326847488</v>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>Still Residual</t>
-        </is>
-      </c>
-      <c r="I320" t="n">
-        <v>980</v>
+        <v>1022</v>
       </c>
     </row>
   </sheetData>
@@ -12026,7 +11795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12078,666 +11847,172 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAD Curncy</t>
+          <t>BABA US Equity</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44111</v>
+        <v>44446</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>44235</v>
+        <v>45923</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>1477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2632873394351858</v>
+        <v>0.5474875512866419</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43521</v>
+        <v>44558</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>43637</v>
+        <v>45281</v>
       </c>
       <c r="D4" t="n">
-        <v>116</v>
+        <v>723</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001964416139246338</v>
+        <v>0.5092618261890409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43641</v>
+        <v>44334</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>43707</v>
+        <v>44708</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>374</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3878927770042555</v>
+        <v>0.4042329336493665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>43713</v>
+        <v>44545</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>43951</v>
+        <v>44952</v>
       </c>
       <c r="D6" t="n">
-        <v>238</v>
+        <v>407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001509179929640628</v>
+        <v>0.6843959624037065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>43986</v>
+        <v>44620</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>44085</v>
+        <v>45064</v>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>444</v>
       </c>
       <c r="E7" t="n">
-        <v>7.238301190557532e-07</v>
+        <v>0.2560260324007131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>44088</v>
+        <v>44610</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>44610</v>
+        <v>45436</v>
       </c>
       <c r="D8" t="n">
-        <v>522</v>
+        <v>826</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008251777708662412</v>
+        <v>0.6457146440286845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>44614</v>
+        <v>44881</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45336</v>
+        <v>45356</v>
       </c>
       <c r="D9" t="n">
-        <v>722</v>
+        <v>475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1612095762656547</v>
+        <v>0.2505158017269435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45337</v>
+        <v>43900</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45385</v>
+        <v>44132</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0001897852011505419</v>
+        <v>0.4834538818653537</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HKD Curncy</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>44032</v>
+        <v>43773</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>44172</v>
+        <v>44531</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>758</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06757609380609853</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HKD Curncy</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>44372</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>44442</v>
-      </c>
-      <c r="D12" t="n">
-        <v>70</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.2130721935694165</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HKD Curncy</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>44446</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>45385</v>
-      </c>
-      <c r="D13" t="n">
-        <v>939</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-5.06221859042014e-07</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>43675</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>43810</v>
-      </c>
-      <c r="D14" t="n">
-        <v>135</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0142690742599815</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>43811</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>43894</v>
-      </c>
-      <c r="D15" t="n">
-        <v>83</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.011516593765187</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>43906</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>43971</v>
-      </c>
-      <c r="D16" t="n">
-        <v>65</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.09051575473033632</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>43991</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>44025</v>
-      </c>
-      <c r="D17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.05187143232492531</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>44067</v>
-      </c>
-      <c r="D18" t="n">
-        <v>41</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.07743346053086182</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>44225</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>44266</v>
-      </c>
-      <c r="D19" t="n">
-        <v>41</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.01131133997354291</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>44298</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>44342</v>
-      </c>
-      <c r="D20" t="n">
-        <v>44</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.1330329822073394</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>44364</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>44610</v>
-      </c>
-      <c r="D21" t="n">
-        <v>246</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.002443742261310396</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>44630</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>44690</v>
-      </c>
-      <c r="D22" t="n">
-        <v>60</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.003012984095514021</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>44728</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>44778</v>
-      </c>
-      <c r="D23" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.001416672609090148</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>44781</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>44957</v>
-      </c>
-      <c r="D24" t="n">
-        <v>176</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.008081244977611568</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>44958</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>45079</v>
-      </c>
-      <c r="D25" t="n">
-        <v>121</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.01569686210095401</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45082</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>45282</v>
-      </c>
-      <c r="D26" t="n">
-        <v>200</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.2239422313308192</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45286</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>45357</v>
-      </c>
-      <c r="D27" t="n">
-        <v>71</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.5111178541361689</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>META US Equity</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>44558</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>45281</v>
-      </c>
-      <c r="D28" t="n">
-        <v>723</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.5092618261890409</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NVDA US Equity</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>44334</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>44708</v>
-      </c>
-      <c r="D29" t="n">
-        <v>374</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.4042329336493665</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PINS US Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>44545</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>44952</v>
-      </c>
-      <c r="D30" t="n">
-        <v>407</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6843959624037065</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PLTR US Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>44620</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>45064</v>
-      </c>
-      <c r="D31" t="n">
-        <v>444</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.2560260324007131</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PYPL US Equity</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>44610</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>45436</v>
-      </c>
-      <c r="D32" t="n">
-        <v>826</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.6457146440286845</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SE US Equity</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>44881</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>45356</v>
-      </c>
-      <c r="D33" t="n">
-        <v>475</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.2505158017269435</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SHOP CN Equity</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>43900</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>44132</v>
-      </c>
-      <c r="D34" t="n">
-        <v>232</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.4834538818653537</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TWTR US Equity</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>43773</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="D35" t="n">
-        <v>758</v>
-      </c>
-      <c r="E35" t="n">
         <v>0.5063608440363557</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ZAR Curncy</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>44959</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>45215</v>
-      </c>
-      <c r="D36" t="n">
-        <v>256</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02232509365285203</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ZAR Curncy</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45216</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>45385</v>
-      </c>
-      <c r="D37" t="n">
-        <v>169</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.0003329798795747985</v>
       </c>
     </row>
   </sheetData>
